--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 17:20 UTC</t>
+    <t xml:space="preserve">Generated: 12 September 2026, 18:13 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.43</v>
+        <v>7395.49</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5674.77</v>
+        <v>5674.82</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.2</v>
+        <v>13070.3</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135925</v>
+        <v>135926</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104300</v>
+        <v>104301</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240225</v>
+        <v>240226</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.43</v>
+        <v>7395.49</v>
       </c>
       <c r="C3" t="n">
-        <v>5674.77</v>
+        <v>5674.82</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.2</v>
+        <v>13070.3</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135925</v>
+        <v>135926</v>
       </c>
       <c r="I3" t="n">
-        <v>104300</v>
+        <v>104301</v>
       </c>
       <c r="J3" t="n">
-        <v>240225</v>
+        <v>240226</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.78575342466</v>
+        <v>7387.83671232877</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.79232876712</v>
+        <v>5668.83479452055</v>
       </c>
       <c r="D4" t="n">
-        <v>13039.538630137</v>
+        <v>13039.6235616438</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135607</v>
+        <v>135608</v>
       </c>
       <c r="I4" t="n">
-        <v>104054</v>
+        <v>104055</v>
       </c>
       <c r="J4" t="n">
-        <v>239661</v>
+        <v>239663</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.24287671233</v>
+        <v>7366.26835616438</v>
       </c>
       <c r="C5" t="n">
-        <v>5651.94616438356</v>
+        <v>5651.96739726027</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.1293150685</v>
+        <v>12953.1717808219</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -899,7 +899,7 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>134140</v>
+        <v>134139</v>
       </c>
       <c r="I7" t="n">
         <v>102927</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 18:13 UTC</t>
+    <t xml:space="preserve">Generated: 12 September 2026, 18:35 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.49</v>
+        <v>7395.51</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5674.82</v>
+        <v>5674.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.3</v>
+        <v>13070.35</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>104301</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240226</v>
+        <v>240227</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.49</v>
+        <v>7395.51</v>
       </c>
       <c r="C3" t="n">
-        <v>5674.82</v>
+        <v>5674.84</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.3</v>
+        <v>13070.35</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -741,7 +741,7 @@
         <v>104301</v>
       </c>
       <c r="J3" t="n">
-        <v>240226</v>
+        <v>240227</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.83671232877</v>
+        <v>7387.85369863014</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.83479452055</v>
+        <v>5668.85178082192</v>
       </c>
       <c r="D4" t="n">
-        <v>13039.6235616438</v>
+        <v>13039.6660273973</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.26835616438</v>
+        <v>7366.27684931507</v>
       </c>
       <c r="C5" t="n">
-        <v>5651.96739726027</v>
+        <v>5651.97589041096</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.1717808219</v>
+        <v>12953.1930136986</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134883</v>
+        <v>134884</v>
       </c>
       <c r="I5" t="n">
         <v>103493</v>
       </c>
       <c r="J5" t="n">
-        <v>238376</v>
+        <v>238377</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 18:35 UTC</t>
+    <t xml:space="preserve">Generated: 12 September 2026, 19:52 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.51</v>
+        <v>7395.59</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5674.84</v>
+        <v>5674.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.35</v>
+        <v>13070.49</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135926</v>
+        <v>135927</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104301</v>
+        <v>104302</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240227</v>
+        <v>240229</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.51</v>
+        <v>7395.59</v>
       </c>
       <c r="C3" t="n">
-        <v>5674.84</v>
+        <v>5674.9</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.35</v>
+        <v>13070.49</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135926</v>
+        <v>135927</v>
       </c>
       <c r="I3" t="n">
-        <v>104301</v>
+        <v>104302</v>
       </c>
       <c r="J3" t="n">
-        <v>240227</v>
+        <v>240229</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.85369863014</v>
+        <v>7387.92164383562</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.85178082192</v>
+        <v>5668.90273972603</v>
       </c>
       <c r="D4" t="n">
-        <v>13039.6660273973</v>
+        <v>13039.7849315068</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135608</v>
+        <v>135609</v>
       </c>
       <c r="I4" t="n">
-        <v>104055</v>
+        <v>104056</v>
       </c>
       <c r="J4" t="n">
-        <v>239663</v>
+        <v>239665</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.27684931507</v>
+        <v>7366.31082191781</v>
       </c>
       <c r="C5" t="n">
-        <v>5651.97589041096</v>
+        <v>5652.00136986301</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.1930136986</v>
+        <v>12953.2524657534</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -864,7 +864,7 @@
         <v>102930</v>
       </c>
       <c r="J6" t="n">
-        <v>237087</v>
+        <v>237086</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -902,7 +902,7 @@
         <v>134139</v>
       </c>
       <c r="I7" t="n">
-        <v>102927</v>
+        <v>102926</v>
       </c>
       <c r="J7" t="n">
         <v>237066</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 19:52 UTC</t>
+    <t xml:space="preserve">Generated: 12 September 2026, 20:38 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.59</v>
+        <v>7395.64</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5674.9</v>
+        <v>5674.94</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.49</v>
+        <v>13070.58</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135927</v>
+        <v>135928</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>104302</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240229</v>
+        <v>240230</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.59</v>
+        <v>7395.64</v>
       </c>
       <c r="C3" t="n">
-        <v>5674.9</v>
+        <v>5674.94</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.49</v>
+        <v>13070.58</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135927</v>
+        <v>135928</v>
       </c>
       <c r="I3" t="n">
         <v>104302</v>
       </c>
       <c r="J3" t="n">
-        <v>240229</v>
+        <v>240230</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.92164383562</v>
+        <v>7387.96410958904</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.90273972603</v>
+        <v>5668.93671232877</v>
       </c>
       <c r="D4" t="n">
-        <v>13039.7849315068</v>
+        <v>13039.861369863</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135609</v>
+        <v>135610</v>
       </c>
       <c r="I4" t="n">
         <v>104056</v>
       </c>
       <c r="J4" t="n">
-        <v>239665</v>
+        <v>239666</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.31082191781</v>
+        <v>7366.33205479452</v>
       </c>
       <c r="C5" t="n">
-        <v>5652.00136986301</v>
+        <v>5652.01835616438</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.2524657534</v>
+        <v>12953.2906849315</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -823,7 +823,7 @@
         <v>103493</v>
       </c>
       <c r="J5" t="n">
-        <v>238377</v>
+        <v>238378</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -861,7 +861,7 @@
         <v>134157</v>
       </c>
       <c r="I6" t="n">
-        <v>102930</v>
+        <v>102929</v>
       </c>
       <c r="J6" t="n">
         <v>237086</v>
@@ -905,7 +905,7 @@
         <v>102926</v>
       </c>
       <c r="J7" t="n">
-        <v>237066</v>
+        <v>237065</v>
       </c>
       <c r="K7" t="n">
         <v>40</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 20:38 UTC</t>
+    <t xml:space="preserve">Generated: 12 September 2026, 22:43 UTC</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.64</v>
+        <v>7395.78</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5674.94</v>
+        <v>5675.04</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.58</v>
+        <v>13070.82</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135928</v>
+        <v>135930</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104302</v>
+        <v>104304</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240230</v>
+        <v>240234</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.64</v>
+        <v>7395.78</v>
       </c>
       <c r="C3" t="n">
-        <v>5674.94</v>
+        <v>5675.04</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.58</v>
+        <v>13070.82</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135928</v>
+        <v>135930</v>
       </c>
       <c r="I3" t="n">
-        <v>104302</v>
+        <v>104304</v>
       </c>
       <c r="J3" t="n">
-        <v>240230</v>
+        <v>240234</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.96410958904</v>
+        <v>7388.08301369863</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.93671232877</v>
+        <v>5669.02164383562</v>
       </c>
       <c r="D4" t="n">
-        <v>13039.861369863</v>
+        <v>13040.0652054795</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135610</v>
+        <v>135611</v>
       </c>
       <c r="I4" t="n">
-        <v>104056</v>
+        <v>104057</v>
       </c>
       <c r="J4" t="n">
-        <v>239666</v>
+        <v>239669</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.33205479452</v>
+        <v>7366.39150684932</v>
       </c>
       <c r="C5" t="n">
-        <v>5652.01835616438</v>
+        <v>5652.06082191781</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.2906849315</v>
+        <v>12953.3926027397</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134884</v>
+        <v>134885</v>
       </c>
       <c r="I5" t="n">
-        <v>103493</v>
+        <v>103494</v>
       </c>
       <c r="J5" t="n">
-        <v>238378</v>
+        <v>238379</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -858,13 +858,13 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>134157</v>
+        <v>134156</v>
       </c>
       <c r="I6" t="n">
         <v>102929</v>
       </c>
       <c r="J6" t="n">
-        <v>237086</v>
+        <v>237085</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -19,7 +19,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Snapshot</t>
   </si>
   <si>
-    <t xml:space="preserve">As at 12th September 2026</t>
+    <t xml:space="preserve">As at 13th September 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 12 September 2026, 22:43 UTC</t>
+    <t xml:space="preserve">Generated: 13 September 2026, 05:35 EAT</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7395.78</v>
+        <v>7396.03</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5675.04</v>
+        <v>5675.24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13070.82</v>
+        <v>13071.26</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135930</v>
+        <v>135934</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104304</v>
+        <v>104307</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240234</v>
+        <v>240240</v>
       </c>
     </row>
     <row r="8">
@@ -714,16 +714,16 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="n">
-        <v>7395.78</v>
+        <v>7396.03</v>
       </c>
       <c r="C3" t="n">
-        <v>5675.04</v>
+        <v>5675.24</v>
       </c>
       <c r="D3" t="n">
-        <v>13070.82</v>
+        <v>13071.26</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135930</v>
+        <v>135934</v>
       </c>
       <c r="I3" t="n">
-        <v>104304</v>
+        <v>104307</v>
       </c>
       <c r="J3" t="n">
-        <v>240234</v>
+        <v>240240</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7388.08301369863</v>
+        <v>7387.70621621622</v>
       </c>
       <c r="C4" t="n">
-        <v>5669.02164383562</v>
+        <v>5668.73081081081</v>
       </c>
       <c r="D4" t="n">
-        <v>13040.0652054795</v>
+        <v>13038.0913513514</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135611</v>
+        <v>135590</v>
       </c>
       <c r="I4" t="n">
-        <v>104057</v>
+        <v>104041</v>
       </c>
       <c r="J4" t="n">
-        <v>239669</v>
+        <v>239631</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.39150684932</v>
+        <v>7366.20310810811</v>
       </c>
       <c r="C5" t="n">
-        <v>5652.06082191781</v>
+        <v>5651.91540540541</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.3926027397</v>
+        <v>12952.4056756757</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134885</v>
+        <v>134874</v>
       </c>
       <c r="I5" t="n">
-        <v>103494</v>
+        <v>103485</v>
       </c>
       <c r="J5" t="n">
-        <v>238379</v>
+        <v>238359</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -864,7 +864,7 @@
         <v>102929</v>
       </c>
       <c r="J6" t="n">
-        <v>237085</v>
+        <v>237084</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -899,13 +899,13 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>134139</v>
+        <v>134138</v>
       </c>
       <c r="I7" t="n">
         <v>102926</v>
       </c>
       <c r="J7" t="n">
-        <v>237065</v>
+        <v>237064</v>
       </c>
       <c r="K7" t="n">
         <v>40</v>
@@ -940,13 +940,13 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>132087</v>
+        <v>132086</v>
       </c>
       <c r="I8" t="n">
         <v>102544</v>
       </c>
       <c r="J8" t="n">
-        <v>234631</v>
+        <v>234630</v>
       </c>
       <c r="K8" t="n">
         <v>40</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 13 September 2026, 05:35 EAT</t>
+    <t xml:space="preserve">Generated: 14 September 2026, 01:43 EAT</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7396.03</v>
+        <v>7397.34</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5675.24</v>
+        <v>5676.24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13071.26</v>
+        <v>13073.57</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135934</v>
+        <v>135953</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104307</v>
+        <v>104321</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240240</v>
+        <v>240274</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +717,13 @@
         <v>46278</v>
       </c>
       <c r="B3" t="n">
-        <v>7396.03</v>
+        <v>7397.34</v>
       </c>
       <c r="C3" t="n">
-        <v>5675.24</v>
+        <v>5676.24</v>
       </c>
       <c r="D3" t="n">
-        <v>13071.26</v>
+        <v>13073.57</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135934</v>
+        <v>135953</v>
       </c>
       <c r="I3" t="n">
-        <v>104307</v>
+        <v>104321</v>
       </c>
       <c r="J3" t="n">
-        <v>240240</v>
+        <v>240274</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7387.70621621622</v>
+        <v>7388.80378378378</v>
       </c>
       <c r="C4" t="n">
-        <v>5668.73081081081</v>
+        <v>5669.56864864865</v>
       </c>
       <c r="D4" t="n">
-        <v>13038.0913513514</v>
+        <v>13040.0267567568</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135590</v>
+        <v>135605</v>
       </c>
       <c r="I4" t="n">
-        <v>104041</v>
+        <v>104052</v>
       </c>
       <c r="J4" t="n">
-        <v>239631</v>
+        <v>239657</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.20310810811</v>
+        <v>7366.75189189189</v>
       </c>
       <c r="C5" t="n">
-        <v>5651.91540540541</v>
+        <v>5652.33432432432</v>
       </c>
       <c r="D5" t="n">
-        <v>12952.4056756757</v>
+        <v>12953.3733783784</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134874</v>
+        <v>134880</v>
       </c>
       <c r="I5" t="n">
-        <v>103485</v>
+        <v>103490</v>
       </c>
       <c r="J5" t="n">
-        <v>238359</v>
+        <v>238369</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -858,13 +858,13 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>134156</v>
+        <v>134152</v>
       </c>
       <c r="I6" t="n">
-        <v>102929</v>
+        <v>102926</v>
       </c>
       <c r="J6" t="n">
-        <v>237084</v>
+        <v>237078</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -899,13 +899,13 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>134138</v>
+        <v>134135</v>
       </c>
       <c r="I7" t="n">
-        <v>102926</v>
+        <v>102923</v>
       </c>
       <c r="J7" t="n">
-        <v>237064</v>
+        <v>237058</v>
       </c>
       <c r="K7" t="n">
         <v>40</v>
@@ -940,13 +940,13 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>132086</v>
+        <v>132085</v>
       </c>
       <c r="I8" t="n">
-        <v>102544</v>
+        <v>102542</v>
       </c>
       <c r="J8" t="n">
-        <v>234630</v>
+        <v>234627</v>
       </c>
       <c r="K8" t="n">
         <v>40</v>
@@ -981,13 +981,13 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>131112</v>
+        <v>131111</v>
       </c>
       <c r="I9" t="n">
-        <v>102282</v>
+        <v>102281</v>
       </c>
       <c r="J9" t="n">
-        <v>233394</v>
+        <v>233392</v>
       </c>
       <c r="K9" t="n">
         <v>40</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -19,7 +19,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Snapshot</t>
   </si>
   <si>
-    <t xml:space="preserve">As at 13th September 2026</t>
+    <t xml:space="preserve">As at 14th September 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 14 September 2026, 01:43 EAT</t>
+    <t xml:space="preserve">Generated: 14 September 2026, 10:25 EAT</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7397.34</v>
+        <v>7397.9</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5676.24</v>
+        <v>5676.67</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13073.57</v>
+        <v>13074.57</v>
       </c>
     </row>
     <row r="6">
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135953</v>
+        <v>135961</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104321</v>
+        <v>104327</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240274</v>
+        <v>240288</v>
       </c>
     </row>
     <row r="8">
@@ -714,16 +714,16 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="n">
-        <v>7397.34</v>
+        <v>7397.9</v>
       </c>
       <c r="C3" t="n">
-        <v>5676.24</v>
+        <v>5676.67</v>
       </c>
       <c r="D3" t="n">
-        <v>13073.57</v>
+        <v>13074.57</v>
       </c>
       <c r="E3" t="n">
         <v>57</v>
@@ -735,13 +735,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135953</v>
+        <v>135961</v>
       </c>
       <c r="I3" t="n">
-        <v>104321</v>
+        <v>104327</v>
       </c>
       <c r="J3" t="n">
-        <v>240274</v>
+        <v>240288</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -758,13 +758,13 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7388.80378378378</v>
+        <v>7388.67866666667</v>
       </c>
       <c r="C4" t="n">
-        <v>5669.56864864865</v>
+        <v>5669.46453333333</v>
       </c>
       <c r="D4" t="n">
-        <v>13040.0267567568</v>
+        <v>13038.5426666667</v>
       </c>
       <c r="E4" t="n">
         <v>57</v>
@@ -776,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135605</v>
+        <v>135587</v>
       </c>
       <c r="I4" t="n">
-        <v>104052</v>
+        <v>104039</v>
       </c>
       <c r="J4" t="n">
-        <v>239657</v>
+        <v>239626</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -799,13 +799,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.75189189189</v>
+        <v>7366.68933333333</v>
       </c>
       <c r="C5" t="n">
-        <v>5652.33432432432</v>
+        <v>5652.28226666667</v>
       </c>
       <c r="D5" t="n">
-        <v>12953.3733783784</v>
+        <v>12952.6313333333</v>
       </c>
       <c r="E5" t="n">
         <v>57</v>
@@ -817,13 +817,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134880</v>
+        <v>134870</v>
       </c>
       <c r="I5" t="n">
-        <v>103490</v>
+        <v>103483</v>
       </c>
       <c r="J5" t="n">
-        <v>238369</v>
+        <v>238353</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -858,13 +858,13 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>134152</v>
+        <v>134151</v>
       </c>
       <c r="I6" t="n">
-        <v>102926</v>
+        <v>102925</v>
       </c>
       <c r="J6" t="n">
-        <v>237078</v>
+        <v>237076</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -899,13 +899,13 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>134135</v>
+        <v>134133</v>
       </c>
       <c r="I7" t="n">
-        <v>102923</v>
+        <v>102922</v>
       </c>
       <c r="J7" t="n">
-        <v>237058</v>
+        <v>237055</v>
       </c>
       <c r="K7" t="n">
         <v>40</v>
@@ -940,13 +940,13 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>132085</v>
+        <v>132084</v>
       </c>
       <c r="I8" t="n">
         <v>102542</v>
       </c>
       <c r="J8" t="n">
-        <v>234627</v>
+        <v>234626</v>
       </c>
       <c r="K8" t="n">
         <v>40</v>
@@ -981,7 +981,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>131111</v>
+        <v>131110</v>
       </c>
       <c r="I9" t="n">
         <v>102281</v>

--- a/docs/kenya_public_debt_data.xlsx
+++ b/docs/kenya_public_debt_data.xlsx
@@ -19,7 +19,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Snapshot</t>
   </si>
   <si>
-    <t xml:space="preserve">As at 14th September 2026</t>
+    <t xml:space="preserve">As at 25th October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Kenya Public Debt -- Notes &amp; Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated: 14 September 2026, 10:25 EAT</t>
+    <t xml:space="preserve">Generated: 25 October 2026, 19:05 EAT</t>
   </si>
   <si>
     <t xml:space="preserve">Report: IEA Kenya Quarterly Macro &amp; Public Debt Report</t>
@@ -103,13 +103,13 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount: Source: Kenya Debt Counter live API (api.kenyadebtcounter.or.ke)</t>
+    <t xml:space="preserve">Amount: Source: Kenya Debt Counter (kenyadebtcounter.vercel.app)</t>
   </si>
   <si>
-    <t xml:space="preserve">Per Capita: Source: Kenya Debt Counter live API</t>
+    <t xml:space="preserve">Per Capita: Source: Kenya Debt Counter (kenyadebtcounter.vercel.app)</t>
   </si>
   <si>
-    <t xml:space="preserve">As % of GDP: Source: Kenya Debt Counter live API</t>
+    <t xml:space="preserve">As % of GDP: Source: Kenya Debt Counter (kenyadebtcounter.vercel.app)</t>
   </si>
   <si>
     <t xml:space="preserve">Methodology note</t>
@@ -118,10 +118,10 @@
     <t xml:space="preserve">Where the published Total and the Domestic/External split do not sum exactly (a fraction of a percent, typically an FX-valuation timing difference on external debt), Domestic is scaled onto the published Total (Domestic' = Domestic x Total / (Domestic+External)) and External is taken as the remainder (External' = Total - Domestic'). This keeps the published Total exact and preserves the source's own domestic:external ratio to the last decimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Largest such gap closed in the Per Capita series: 0.88%.</t>
+    <t xml:space="preserve">Largest such gap closed in the Per Capita series: 0.00%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Largest such gap closed in the As % of GDP series: 0.88%.</t>
+    <t xml:space="preserve">Largest such gap closed in the As % of GDP series: 0.00%.</t>
   </si>
 </sst>
 </file>
@@ -548,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7397.9</v>
+        <v>7584.49</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5676.67</v>
+        <v>5972.89</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13074.57</v>
+        <v>13557.38</v>
       </c>
     </row>
     <row r="6">
@@ -562,10 +562,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>100</v>
@@ -576,13 +576,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>135961</v>
+        <v>139148</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>104327</v>
+        <v>109581</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>240288</v>
+        <v>248729</v>
       </c>
     </row>
     <row r="8">
@@ -593,10 +593,10 @@
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -714,43 +714,43 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46279</v>
+        <v>46320</v>
       </c>
       <c r="B3" t="n">
-        <v>7397.9</v>
+        <v>7584.49</v>
       </c>
       <c r="C3" t="n">
-        <v>5676.67</v>
+        <v>5972.89</v>
       </c>
       <c r="D3" t="n">
-        <v>13074.57</v>
+        <v>13557.38</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>135961</v>
+        <v>139148</v>
       </c>
       <c r="I3" t="n">
-        <v>104327</v>
+        <v>109581</v>
       </c>
       <c r="J3" t="n">
-        <v>240288</v>
+        <v>248729</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -758,40 +758,40 @@
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>7388.67866666667</v>
+        <v>7490.61</v>
       </c>
       <c r="C4" t="n">
-        <v>5669.46453333333</v>
+        <v>5898.95</v>
       </c>
       <c r="D4" t="n">
-        <v>13038.5426666667</v>
+        <v>13389.56</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>135587</v>
+        <v>137751</v>
       </c>
       <c r="I4" t="n">
-        <v>104039</v>
+        <v>108481</v>
       </c>
       <c r="J4" t="n">
-        <v>239626</v>
+        <v>246232</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -799,16 +799,16 @@
         <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>7366.68933333333</v>
+        <v>7438.23</v>
       </c>
       <c r="C5" t="n">
-        <v>5652.28226666667</v>
+        <v>5857.7</v>
       </c>
       <c r="D5" t="n">
-        <v>12952.6313333333</v>
+        <v>13295.93</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>44</v>
@@ -817,22 +817,22 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>134870</v>
+        <v>136978</v>
       </c>
       <c r="I5" t="n">
-        <v>103483</v>
+        <v>107872</v>
       </c>
       <c r="J5" t="n">
-        <v>238353</v>
+        <v>244850</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -840,16 +840,16 @@
         <v>46204</v>
       </c>
       <c r="B6" t="n">
-        <v>7344.7</v>
+        <v>7385.84</v>
       </c>
       <c r="C6" t="n">
-        <v>5635.1</v>
+        <v>5816.45</v>
       </c>
       <c r="D6" t="n">
-        <v>12866.72</v>
+        <v>13202.29</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
         <v>44</v>
@@ -858,63 +858,63 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>134151</v>
+        <v>136202</v>
       </c>
       <c r="I6" t="n">
-        <v>102925</v>
+        <v>107261</v>
       </c>
       <c r="J6" t="n">
-        <v>237076</v>
+        <v>243463</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46203</v>
+        <v>46174</v>
       </c>
       <c r="B7" t="n">
-        <v>7279.47</v>
+        <v>7327.2</v>
       </c>
       <c r="C7" t="n">
-        <v>5585.61</v>
+        <v>5770.27</v>
       </c>
       <c r="D7" t="n">
-        <v>12865.07</v>
+        <v>13097.47</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>134133</v>
+        <v>135309</v>
       </c>
       <c r="I7" t="n">
-        <v>102922</v>
+        <v>106557</v>
       </c>
       <c r="J7" t="n">
-        <v>237055</v>
+        <v>241866</v>
       </c>
       <c r="K7" t="n">
         <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -922,16 +922,16 @@
         <v>46143</v>
       </c>
       <c r="B8" t="n">
-        <v>7192.32</v>
+        <v>7238.52</v>
       </c>
       <c r="C8" t="n">
-        <v>5583.68</v>
+        <v>5657.3</v>
       </c>
       <c r="D8" t="n">
-        <v>12701.57</v>
+        <v>12895.82</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
         <v>44</v>
@@ -940,13 +940,13 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>132084</v>
+        <v>133857</v>
       </c>
       <c r="I8" t="n">
-        <v>102542</v>
+        <v>104616</v>
       </c>
       <c r="J8" t="n">
-        <v>234626</v>
+        <v>238473</v>
       </c>
       <c r="K8" t="n">
         <v>40</v>
@@ -963,13 +963,13 @@
         <v>46113</v>
       </c>
       <c r="B9" t="n">
-        <v>7124.57</v>
+        <v>7185.21</v>
       </c>
       <c r="C9" t="n">
-        <v>5557.98</v>
+        <v>5670.63</v>
       </c>
       <c r="D9" t="n">
-        <v>12619</v>
+        <v>12855.84</v>
       </c>
       <c r="E9" t="n">
         <v>56</v>
@@ -981,13 +981,13 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>131110</v>
+        <v>133055</v>
       </c>
       <c r="I9" t="n">
-        <v>102281</v>
+        <v>105009</v>
       </c>
       <c r="J9" t="n">
-        <v>233392</v>
+        <v>238064</v>
       </c>
       <c r="K9" t="n">
         <v>40</v>
@@ -1004,13 +1004,13 @@
         <v>46082</v>
       </c>
       <c r="B10" t="n">
-        <v>7060.58</v>
+        <v>7149.16</v>
       </c>
       <c r="C10" t="n">
-        <v>5532.27</v>
+        <v>5683.22</v>
       </c>
       <c r="D10" t="n">
-        <v>12536.43</v>
+        <v>12832.39</v>
       </c>
       <c r="E10" t="n">
         <v>56</v>
@@ -1022,22 +1022,22 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>130170</v>
+        <v>132572</v>
       </c>
       <c r="I10" t="n">
-        <v>101994</v>
+        <v>105388</v>
       </c>
       <c r="J10" t="n">
-        <v>232164</v>
+        <v>237960</v>
       </c>
       <c r="K10" t="n">
         <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -1045,40 +1045,40 @@
         <v>46054</v>
       </c>
       <c r="B11" t="n">
-        <v>6989.65</v>
+        <v>7064.12</v>
       </c>
       <c r="C11" t="n">
-        <v>5506.56</v>
+        <v>5779.07</v>
       </c>
       <c r="D11" t="n">
-        <v>12453.85</v>
+        <v>12843.19</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>129164</v>
+        <v>131177</v>
       </c>
       <c r="I11" t="n">
-        <v>101757</v>
+        <v>107314</v>
       </c>
       <c r="J11" t="n">
-        <v>230921</v>
+        <v>238491</v>
       </c>
       <c r="K11" t="n">
         <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1086,13 +1086,13 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>6909.04</v>
+        <v>6891.47</v>
       </c>
       <c r="C12" t="n">
-        <v>5480.85</v>
+        <v>5506.99</v>
       </c>
       <c r="D12" t="n">
-        <v>12374.76</v>
+        <v>12398.46</v>
       </c>
       <c r="E12" t="n">
         <v>56</v>
@@ -1104,13 +1104,13 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>128128</v>
+        <v>128149</v>
       </c>
       <c r="I12" t="n">
-        <v>101643</v>
+        <v>102404</v>
       </c>
       <c r="J12" t="n">
-        <v>229771</v>
+        <v>230553</v>
       </c>
       <c r="K12" t="n">
         <v>39</v>
@@ -1119,7 +1119,7 @@
         <v>31</v>
       </c>
       <c r="M12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -1127,13 +1127,13 @@
         <v>45992</v>
       </c>
       <c r="B13" t="n">
-        <v>6837.51</v>
+        <v>6838.66</v>
       </c>
       <c r="C13" t="n">
         <v>5461.97</v>
       </c>
       <c r="D13" t="n">
-        <v>12299.48</v>
+        <v>12300.63</v>
       </c>
       <c r="E13" t="n">
         <v>56</v>
@@ -1145,13 +1145,13 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>127134</v>
+        <v>127343</v>
       </c>
       <c r="I13" t="n">
-        <v>101558</v>
+        <v>101708</v>
       </c>
       <c r="J13" t="n">
-        <v>228692</v>
+        <v>229051</v>
       </c>
       <c r="K13" t="n">
         <v>39</v>
@@ -1160,7 +1160,7 @@
         <v>31</v>
       </c>
       <c r="M13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1186,22 +1186,22 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>126341</v>
+        <v>126526</v>
       </c>
       <c r="I14" t="n">
-        <v>101834</v>
+        <v>101984</v>
       </c>
       <c r="J14" t="n">
-        <v>228175</v>
+        <v>228510</v>
       </c>
       <c r="K14" t="n">
         <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1227,22 +1227,22 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>125627</v>
+        <v>125810</v>
       </c>
       <c r="I15" t="n">
-        <v>101655</v>
+        <v>101803</v>
       </c>
       <c r="J15" t="n">
-        <v>227282</v>
+        <v>227612</v>
       </c>
       <c r="K15" t="n">
         <v>39</v>
       </c>
       <c r="L15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1268,22 +1268,22 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>124363</v>
+        <v>124542</v>
       </c>
       <c r="I16" t="n">
-        <v>100707</v>
+        <v>100853</v>
       </c>
       <c r="J16" t="n">
-        <v>225070</v>
+        <v>225395</v>
       </c>
       <c r="K16" t="n">
         <v>39</v>
       </c>
       <c r="L16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -1309,22 +1309,22 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>122744</v>
+        <v>122919</v>
       </c>
       <c r="I17" t="n">
-        <v>101031</v>
+        <v>101175</v>
       </c>
       <c r="J17" t="n">
-        <v>223776</v>
+        <v>224095</v>
       </c>
       <c r="K17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
         <v>32</v>
       </c>
       <c r="M17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -1350,13 +1350,13 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>119579</v>
+        <v>119747</v>
       </c>
       <c r="I18" t="n">
-        <v>100837</v>
+        <v>100979</v>
       </c>
       <c r="J18" t="n">
-        <v>220415</v>
+        <v>220726</v>
       </c>
       <c r="K18" t="n">
         <v>38</v>
@@ -1365,7 +1365,7 @@
         <v>32</v>
       </c>
       <c r="M18" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -1391,22 +1391,22 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>118607</v>
+        <v>118776</v>
       </c>
       <c r="I19" t="n">
-        <v>102845</v>
+        <v>102992</v>
       </c>
       <c r="J19" t="n">
-        <v>221453</v>
+        <v>221768</v>
       </c>
       <c r="K19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M19" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1432,13 +1432,13 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>116486</v>
+        <v>116653</v>
       </c>
       <c r="I20" t="n">
-        <v>99673</v>
+        <v>99816</v>
       </c>
       <c r="J20" t="n">
-        <v>216159</v>
+        <v>216469</v>
       </c>
       <c r="K20" t="n">
         <v>37</v>
@@ -1473,13 +1473,13 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>115909</v>
+        <v>116076</v>
       </c>
       <c r="I21" t="n">
-        <v>100154</v>
+        <v>100299</v>
       </c>
       <c r="J21" t="n">
-        <v>216063</v>
+        <v>216375</v>
       </c>
       <c r="K21" t="n">
         <v>37</v>
@@ -1514,13 +1514,13 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>115368</v>
+        <v>115536</v>
       </c>
       <c r="I22" t="n">
-        <v>98639</v>
+        <v>98783</v>
       </c>
       <c r="J22" t="n">
-        <v>214008</v>
+        <v>214319</v>
       </c>
       <c r="K22" t="n">
         <v>37</v>
@@ -1555,13 +1555,13 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>114317</v>
+        <v>114492</v>
       </c>
       <c r="I23" t="n">
-        <v>95627</v>
+        <v>95774</v>
       </c>
       <c r="J23" t="n">
-        <v>209944</v>
+        <v>210266</v>
       </c>
       <c r="K23" t="n">
         <v>37</v>
@@ -1596,22 +1596,22 @@
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>111940</v>
+        <v>112104</v>
       </c>
       <c r="I24" t="n">
-        <v>95994</v>
+        <v>96135</v>
       </c>
       <c r="J24" t="n">
-        <v>207935</v>
+        <v>208239</v>
       </c>
       <c r="K24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L24" t="n">
         <v>31</v>
       </c>
       <c r="M24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -1637,13 +1637,13 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>110974</v>
+        <v>111136</v>
       </c>
       <c r="I25" t="n">
-        <v>95632</v>
+        <v>95772</v>
       </c>
       <c r="J25" t="n">
-        <v>206605</v>
+        <v>206908</v>
       </c>
       <c r="K25" t="n">
         <v>36</v>
@@ -1652,7 +1652,7 @@
         <v>31</v>
       </c>
       <c r="M25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -1678,13 +1678,13 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>110015</v>
+        <v>110176</v>
       </c>
       <c r="I26" t="n">
-        <v>97304</v>
+        <v>97447</v>
       </c>
       <c r="J26" t="n">
-        <v>207319</v>
+        <v>207623</v>
       </c>
       <c r="K26" t="n">
         <v>36</v>
@@ -1719,13 +1719,13 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>107977</v>
+        <v>108134</v>
       </c>
       <c r="I27" t="n">
-        <v>97105</v>
+        <v>97247</v>
       </c>
       <c r="J27" t="n">
-        <v>205082</v>
+        <v>205381</v>
       </c>
       <c r="K27" t="n">
         <v>36</v>
@@ -1760,13 +1760,13 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>106387</v>
+        <v>106542</v>
       </c>
       <c r="I28" t="n">
-        <v>98537</v>
+        <v>98680</v>
       </c>
       <c r="J28" t="n">
-        <v>204924</v>
+        <v>205222</v>
       </c>
       <c r="K28" t="n">
         <v>35</v>
@@ -1801,13 +1801,13 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>105714</v>
+        <v>105867</v>
       </c>
       <c r="I29" t="n">
-        <v>98444</v>
+        <v>98587</v>
       </c>
       <c r="J29" t="n">
-        <v>204159</v>
+        <v>204454</v>
       </c>
       <c r="K29" t="n">
         <v>35</v>
@@ -1842,13 +1842,13 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>103860</v>
+        <v>104009</v>
       </c>
       <c r="I30" t="n">
-        <v>98333</v>
+        <v>98475</v>
       </c>
       <c r="J30" t="n">
-        <v>202193</v>
+        <v>202483</v>
       </c>
       <c r="K30" t="n">
         <v>35</v>
@@ -1883,13 +1883,13 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>103194</v>
+        <v>103344</v>
       </c>
       <c r="I31" t="n">
-        <v>98245</v>
+        <v>98388</v>
       </c>
       <c r="J31" t="n">
-        <v>201440</v>
+        <v>201731</v>
       </c>
       <c r="K31" t="n">
         <v>35</v>
@@ -1924,13 +1924,13 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>101616</v>
+        <v>101764</v>
       </c>
       <c r="I32" t="n">
-        <v>97765</v>
+        <v>97908</v>
       </c>
       <c r="J32" t="n">
-        <v>199381</v>
+        <v>199672</v>
       </c>
       <c r="K32" t="n">
         <v>34</v>
@@ -1939,7 +1939,7 @@
         <v>33</v>
       </c>
       <c r="M32" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33">
@@ -1965,13 +1965,13 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>101835</v>
+        <v>101985</v>
       </c>
       <c r="I33" t="n">
-        <v>99446</v>
+        <v>99592</v>
       </c>
       <c r="J33" t="n">
-        <v>201281</v>
+        <v>201576</v>
       </c>
       <c r="K33" t="n">
         <v>35</v>
@@ -1980,7 +1980,7 @@
         <v>34</v>
       </c>
       <c r="M33" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
@@ -2006,13 +2006,13 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>100287</v>
+        <v>100434</v>
       </c>
       <c r="I34" t="n">
-        <v>98912</v>
+        <v>99057</v>
       </c>
       <c r="J34" t="n">
-        <v>199198</v>
+        <v>199491</v>
       </c>
       <c r="K34" t="n">
         <v>34</v>
@@ -2047,13 +2047,13 @@
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>99756</v>
+        <v>99908</v>
       </c>
       <c r="I35" t="n">
-        <v>108459</v>
+        <v>108624</v>
       </c>
       <c r="J35" t="n">
-        <v>208214</v>
+        <v>208531</v>
       </c>
       <c r="K35" t="n">
         <v>34</v>
@@ -2062,7 +2062,7 @@
         <v>37</v>
       </c>
       <c r="M35" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
@@ -2088,22 +2088,22 @@
         <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>97027</v>
+        <v>97171</v>
       </c>
       <c r="I36" t="n">
-        <v>118920</v>
+        <v>119095</v>
       </c>
       <c r="J36" t="n">
-        <v>215947</v>
+        <v>216266</v>
       </c>
       <c r="K36" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L36" t="n">
         <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
@@ -2129,13 +2129,13 @@
         <v>100</v>
       </c>
       <c r="H37" t="n">
-        <v>97162</v>
+        <v>97305</v>
       </c>
       <c r="I37" t="n">
-        <v>117161</v>
+        <v>117333</v>
       </c>
       <c r="J37" t="n">
-        <v>214322</v>
+        <v>214638</v>
       </c>
       <c r="K37" t="n">
         <v>34</v>
@@ -2144,7 +2144,7 @@
         <v>41</v>
       </c>
       <c r="M37" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
@@ -2170,22 +2170,22 @@
         <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>96159</v>
+        <v>96300</v>
       </c>
       <c r="I38" t="n">
-        <v>113610</v>
+        <v>113778</v>
       </c>
       <c r="J38" t="n">
-        <v>209769</v>
+        <v>210078</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L38" t="n">
         <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
@@ -2211,13 +2211,13 @@
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>94799</v>
+        <v>94938</v>
       </c>
       <c r="I39" t="n">
-        <v>110877</v>
+        <v>111040</v>
       </c>
       <c r="J39" t="n">
-        <v>205676</v>
+        <v>205979</v>
       </c>
       <c r="K39" t="n">
         <v>33</v>
@@ -2226,7 +2226,7 @@
         <v>39</v>
       </c>
       <c r="M39" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
@@ -2252,13 +2252,13 @@
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>94967</v>
+        <v>95106</v>
       </c>
       <c r="I40" t="n">
-        <v>109521</v>
+        <v>109682</v>
       </c>
       <c r="J40" t="n">
-        <v>204488</v>
+        <v>204788</v>
       </c>
       <c r="K40" t="n">
         <v>34</v>
@@ -2267,7 +2267,7 @@
         <v>39</v>
       </c>
       <c r="M40" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
@@ -2293,13 +2293,13 @@
         <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>95061</v>
+        <v>95200</v>
       </c>
       <c r="I41" t="n">
-        <v>108641</v>
+        <v>108800</v>
       </c>
       <c r="J41" t="n">
-        <v>203702</v>
+        <v>204000</v>
       </c>
       <c r="K41" t="n">
         <v>34</v>
@@ -2334,13 +2334,13 @@
         <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>94447</v>
+        <v>94585</v>
       </c>
       <c r="I42" t="n">
-        <v>107414</v>
+        <v>107571</v>
       </c>
       <c r="J42" t="n">
-        <v>201861</v>
+        <v>202155</v>
       </c>
       <c r="K42" t="n">
         <v>34</v>
@@ -2349,7 +2349,7 @@
         <v>39</v>
       </c>
       <c r="M42" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
@@ -2375,13 +2375,13 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>93781</v>
+        <v>93919</v>
       </c>
       <c r="I43" t="n">
-        <v>105706</v>
+        <v>105862</v>
       </c>
       <c r="J43" t="n">
-        <v>199487</v>
+        <v>199781</v>
       </c>
       <c r="K43" t="n">
         <v>34</v>
@@ -2390,7 +2390,7 @@
         <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
@@ -2416,19 +2416,19 @@
         <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>88427</v>
+        <v>88559</v>
       </c>
       <c r="I44" t="n">
-        <v>99846</v>
+        <v>99995</v>
       </c>
       <c r="J44" t="n">
-        <v>188274</v>
+        <v>188555</v>
       </c>
       <c r="K44" t="n">
         <v>32</v>
       </c>
       <c r="L44" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M44" t="n">
         <v>69</v>
@@ -2457,19 +2457,19 @@
         <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>88414</v>
+        <v>88548</v>
       </c>
       <c r="I45" t="n">
-        <v>99122</v>
+        <v>99272</v>
       </c>
       <c r="J45" t="n">
-        <v>187537</v>
+        <v>187820</v>
       </c>
       <c r="K45" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L45" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M45" t="n">
         <v>69</v>
@@ -2498,13 +2498,13 @@
         <v>100</v>
       </c>
       <c r="H46" t="n">
-        <v>88489</v>
+        <v>88624</v>
       </c>
       <c r="I46" t="n">
-        <v>94561</v>
+        <v>94706</v>
       </c>
       <c r="J46" t="n">
-        <v>183051</v>
+        <v>183330</v>
       </c>
       <c r="K46" t="n">
         <v>33</v>
@@ -2539,22 +2539,22 @@
         <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>88846</v>
+        <v>88989</v>
       </c>
       <c r="I47" t="n">
-        <v>91933</v>
+        <v>92081</v>
       </c>
       <c r="J47" t="n">
-        <v>180779</v>
+        <v>181070</v>
       </c>
       <c r="K47" t="n">
         <v>33</v>
       </c>
       <c r="L47" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -2580,22 +2580,22 @@
         <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>88008</v>
+        <v>88144</v>
       </c>
       <c r="I48" t="n">
-        <v>91515</v>
+        <v>91657</v>
       </c>
       <c r="J48" t="n">
-        <v>179523</v>
+        <v>179801</v>
       </c>
       <c r="K48" t="n">
         <v>33</v>
       </c>
       <c r="L48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M48" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
@@ -2621,13 +2621,13 @@
         <v>100</v>
       </c>
       <c r="H49" t="n">
-        <v>87572</v>
+        <v>87708</v>
       </c>
       <c r="I49" t="n">
-        <v>91493</v>
+        <v>91635</v>
       </c>
       <c r="J49" t="n">
-        <v>179065</v>
+        <v>179343</v>
       </c>
       <c r="K49" t="n">
         <v>33</v>
@@ -2662,19 +2662,19 @@
         <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>86977</v>
+        <v>87112</v>
       </c>
       <c r="I50" t="n">
-        <v>87506</v>
+        <v>87642</v>
       </c>
       <c r="J50" t="n">
-        <v>174483</v>
+        <v>174754</v>
       </c>
       <c r="K50" t="n">
         <v>33</v>
       </c>
       <c r="L50" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M50" t="n">
         <v>67</v>
@@ -2703,13 +2703,13 @@
         <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>86127</v>
+        <v>86260</v>
       </c>
       <c r="I51" t="n">
-        <v>85606</v>
+        <v>85739</v>
       </c>
       <c r="J51" t="n">
-        <v>171733</v>
+        <v>171999</v>
       </c>
       <c r="K51" t="n">
         <v>33</v>
@@ -2718,7 +2718,7 @@
         <v>33</v>
       </c>
       <c r="M51" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -2744,22 +2744,22 @@
         <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>85865</v>
+        <v>85997</v>
       </c>
       <c r="I52" t="n">
-        <v>85246</v>
+        <v>85377</v>
       </c>
       <c r="J52" t="n">
-        <v>171111</v>
+        <v>171374</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
         <v>33</v>
       </c>
       <c r="M52" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53">
@@ -2785,19 +2785,19 @@
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>85382</v>
+        <v>85512</v>
       </c>
       <c r="I53" t="n">
-        <v>85238</v>
+        <v>85368</v>
       </c>
       <c r="J53" t="n">
-        <v>170620</v>
+        <v>170880</v>
       </c>
       <c r="K53" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L53" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M53" t="n">
         <v>67</v>
@@ -2826,19 +2826,19 @@
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>85025</v>
+        <v>85153</v>
       </c>
       <c r="I54" t="n">
-        <v>84811</v>
+        <v>84938</v>
       </c>
       <c r="J54" t="n">
-        <v>169836</v>
+        <v>170091</v>
       </c>
       <c r="K54" t="n">
         <v>34</v>
       </c>
       <c r="L54" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M54" t="n">
         <v>67</v>
@@ -2867,13 +2867,13 @@
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>84711</v>
+        <v>84838</v>
       </c>
       <c r="I55" t="n">
-        <v>84760</v>
+        <v>84887</v>
       </c>
       <c r="J55" t="n">
-        <v>169471</v>
+        <v>169725</v>
       </c>
       <c r="K55" t="n">
         <v>34</v>
@@ -2882,7 +2882,7 @@
         <v>34</v>
       </c>
       <c r="M55" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56">
@@ -2908,13 +2908,13 @@
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>84450</v>
+        <v>84576</v>
       </c>
       <c r="I56" t="n">
-        <v>84973</v>
+        <v>85100</v>
       </c>
       <c r="J56" t="n">
-        <v>169423</v>
+        <v>169676</v>
       </c>
       <c r="K56" t="n">
         <v>34</v>
@@ -2949,13 +2949,13 @@
         <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>83750</v>
+        <v>83873</v>
       </c>
       <c r="I57" t="n">
-        <v>84080</v>
+        <v>84204</v>
       </c>
       <c r="J57" t="n">
-        <v>167830</v>
+        <v>168077</v>
       </c>
       <c r="K57" t="n">
         <v>34</v>
@@ -2990,13 +2990,13 @@
         <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>83181</v>
+        <v>83302</v>
       </c>
       <c r="I58" t="n">
-        <v>83534</v>
+        <v>83655</v>
       </c>
       <c r="J58" t="n">
-        <v>166715</v>
+        <v>166957</v>
       </c>
       <c r="K58" t="n">
         <v>34</v>
@@ -3031,13 +3031,13 @@
         <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>83095</v>
+        <v>83221</v>
       </c>
       <c r="I59" t="n">
-        <v>82625</v>
+        <v>82750</v>
       </c>
       <c r="J59" t="n">
-        <v>165720</v>
+        <v>165971</v>
       </c>
       <c r="K59" t="n">
         <v>34</v>
@@ -3046,7 +3046,7 @@
         <v>34</v>
       </c>
       <c r="M59" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
@@ -3072,22 +3072,22 @@
         <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>81809</v>
+        <v>81925</v>
       </c>
       <c r="I60" t="n">
-        <v>82718</v>
+        <v>82835</v>
       </c>
       <c r="J60" t="n">
-        <v>164527</v>
+        <v>164760</v>
       </c>
       <c r="K60" t="n">
         <v>34</v>
       </c>
       <c r="L60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M60" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61">
@@ -3113,13 +3113,13 @@
         <v>100</v>
       </c>
       <c r="H61" t="n">
-        <v>80383</v>
+        <v>80495</v>
       </c>
       <c r="I61" t="n">
-        <v>83214</v>
+        <v>83330</v>
       </c>
       <c r="J61" t="n">
-        <v>163597</v>
+        <v>163826</v>
       </c>
       <c r="K61" t="n">
         <v>34</v>
@@ -3128,7 +3128,7 @@
         <v>35</v>
       </c>
       <c r="M61" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -3154,22 +3154,22 @@
         <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>80020</v>
+        <v>80131</v>
       </c>
       <c r="I62" t="n">
-        <v>82040</v>
+        <v>82154</v>
       </c>
       <c r="J62" t="n">
-        <v>162060</v>
+        <v>162284</v>
       </c>
       <c r="K62" t="n">
         <v>34</v>
       </c>
       <c r="L62" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M62" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
@@ -3195,13 +3195,13 @@
         <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>79169</v>
+        <v>79279</v>
       </c>
       <c r="I63" t="n">
-        <v>81641</v>
+        <v>81753</v>
       </c>
       <c r="J63" t="n">
-        <v>160810</v>
+        <v>161032</v>
       </c>
       <c r="K63" t="n">
         <v>34</v>
@@ -3210,7 +3210,7 @@
         <v>35</v>
       </c>
       <c r="M63" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64">
@@ -3236,13 +3236,13 @@
         <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>78852</v>
+        <v>78962</v>
       </c>
       <c r="I64" t="n">
-        <v>81349</v>
+        <v>81463</v>
       </c>
       <c r="J64" t="n">
-        <v>160201</v>
+        <v>160424</v>
       </c>
       <c r="K64" t="n">
         <v>34</v>
@@ -3251,7 +3251,7 @@
         <v>35</v>
       </c>
       <c r="M64" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
@@ -3277,22 +3277,22 @@
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>77507</v>
+        <v>77616</v>
       </c>
       <c r="I65" t="n">
-        <v>81317</v>
+        <v>81431</v>
       </c>
       <c r="J65" t="n">
-        <v>158823</v>
+        <v>159047</v>
       </c>
       <c r="K65" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L65" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M65" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -3318,22 +3318,22 @@
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>76160</v>
+        <v>76270</v>
       </c>
       <c r="I66" t="n">
-        <v>80748</v>
+        <v>80865</v>
       </c>
       <c r="J66" t="n">
-        <v>156908</v>
+        <v>157135</v>
       </c>
       <c r="K66" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L66" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M66" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67">
@@ -3359,22 +3359,22 @@
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>74358</v>
+        <v>74472</v>
       </c>
       <c r="I67" t="n">
-        <v>80441</v>
+        <v>80564</v>
       </c>
       <c r="J67" t="n">
-        <v>154799</v>
+        <v>155036</v>
       </c>
       <c r="K67" t="n">
         <v>33</v>
       </c>
       <c r="L67" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M67" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
@@ -3400,13 +3400,13 @@
         <v>100</v>
       </c>
       <c r="H68" t="n">
-        <v>74259</v>
+        <v>74380</v>
       </c>
       <c r="I68" t="n">
-        <v>76517</v>
+        <v>76642</v>
       </c>
       <c r="J68" t="n">
-        <v>150776</v>
+        <v>151021</v>
       </c>
       <c r="K68" t="n">
         <v>33</v>
@@ -3415,7 +3415,7 @@
         <v>34</v>
       </c>
       <c r="M68" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
@@ -3441,13 +3441,13 @@
         <v>100</v>
       </c>
       <c r="H69" t="n">
-        <v>73275</v>
+        <v>73403</v>
       </c>
       <c r="I69" t="n">
-        <v>76204</v>
+        <v>76337</v>
       </c>
       <c r="J69" t="n">
-        <v>149480</v>
+        <v>149739</v>
       </c>
       <c r="K69" t="n">
         <v>33</v>
@@ -3456,7 +3456,7 @@
         <v>34</v>
       </c>
       <c r="M69" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
@@ -3482,19 +3482,19 @@
         <v>100</v>
       </c>
       <c r="H70" t="n">
-        <v>72105</v>
+        <v>72238</v>
       </c>
       <c r="I70" t="n">
-        <v>76145</v>
+        <v>76286</v>
       </c>
       <c r="J70" t="n">
-        <v>148250</v>
+        <v>148525</v>
       </c>
       <c r="K70" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L70" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M70" t="n">
         <v>67</v>
@@ -3523,22 +3523,22 @@
         <v>100</v>
       </c>
       <c r="H71" t="n">
-        <v>71421</v>
+        <v>71565</v>
       </c>
       <c r="I71" t="n">
-        <v>77147</v>
+        <v>77303</v>
       </c>
       <c r="J71" t="n">
-        <v>148567</v>
+        <v>148868</v>
       </c>
       <c r="K71" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L71" t="n">
         <v>35</v>
       </c>
       <c r="M71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72">
@@ -3564,22 +3564,22 @@
         <v>100</v>
       </c>
       <c r="H72" t="n">
-        <v>71556</v>
+        <v>71703</v>
       </c>
       <c r="I72" t="n">
-        <v>77372</v>
+        <v>77531</v>
       </c>
       <c r="J72" t="n">
-        <v>148928</v>
+        <v>149234</v>
       </c>
       <c r="K72" t="n">
         <v>33</v>
       </c>
       <c r="L72" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M72" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
@@ -3605,19 +3605,19 @@
         <v>100</v>
       </c>
       <c r="H73" t="n">
-        <v>70767</v>
+        <v>70917</v>
       </c>
       <c r="I73" t="n">
-        <v>76949</v>
+        <v>77112</v>
       </c>
       <c r="J73" t="n">
-        <v>147717</v>
+        <v>148030</v>
       </c>
       <c r="K73" t="n">
         <v>33</v>
       </c>
       <c r="L73" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M73" t="n">
         <v>68</v>
@@ -3646,19 +3646,19 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>70753</v>
+        <v>70906</v>
       </c>
       <c r="I74" t="n">
-        <v>76628</v>
+        <v>76793</v>
       </c>
       <c r="J74" t="n">
-        <v>147381</v>
+        <v>147699</v>
       </c>
       <c r="K74" t="n">
         <v>33</v>
       </c>
       <c r="L74" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M74" t="n">
         <v>68</v>
@@ -3687,13 +3687,13 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>70353</v>
+        <v>70504</v>
       </c>
       <c r="I75" t="n">
-        <v>75399</v>
+        <v>75561</v>
       </c>
       <c r="J75" t="n">
-        <v>145752</v>
+        <v>146065</v>
       </c>
       <c r="K75" t="n">
         <v>33</v>
@@ -3702,7 +3702,7 @@
         <v>35</v>
       </c>
       <c r="M75" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76">
@@ -3728,13 +3728,13 @@
         <v>100</v>
       </c>
       <c r="H76" t="n">
-        <v>70454</v>
+        <v>70601</v>
       </c>
       <c r="I76" t="n">
-        <v>74659</v>
+        <v>74816</v>
       </c>
       <c r="J76" t="n">
-        <v>145113</v>
+        <v>145417</v>
       </c>
       <c r="K76" t="n">
         <v>33</v>
@@ -3743,7 +3743,7 @@
         <v>35</v>
       </c>
       <c r="M76" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77">
@@ -3769,13 +3769,13 @@
         <v>100</v>
       </c>
       <c r="H77" t="n">
-        <v>69455</v>
+        <v>69592</v>
       </c>
       <c r="I77" t="n">
-        <v>74840</v>
+        <v>74988</v>
       </c>
       <c r="J77" t="n">
-        <v>144295</v>
+        <v>144580</v>
       </c>
       <c r="K77" t="n">
         <v>32</v>
@@ -3810,13 +3810,13 @@
         <v>100</v>
       </c>
       <c r="H78" t="n">
-        <v>66937</v>
+        <v>67057</v>
       </c>
       <c r="I78" t="n">
-        <v>74400</v>
+        <v>74533</v>
       </c>
       <c r="J78" t="n">
-        <v>141337</v>
+        <v>141590</v>
       </c>
       <c r="K78" t="n">
         <v>31</v>
@@ -3851,16 +3851,16 @@
         <v>100</v>
       </c>
       <c r="H79" t="n">
-        <v>65108</v>
+        <v>65249</v>
       </c>
       <c r="I79" t="n">
-        <v>72019</v>
+        <v>72176</v>
       </c>
       <c r="J79" t="n">
-        <v>137128</v>
+        <v>137425</v>
       </c>
       <c r="K79" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L79" t="n">
         <v>34</v>
@@ -3892,13 +3892,13 @@
         <v>100</v>
       </c>
       <c r="H80" t="n">
-        <v>64711</v>
+        <v>64871</v>
       </c>
       <c r="I80" t="n">
-        <v>71757</v>
+        <v>71934</v>
       </c>
       <c r="J80" t="n">
-        <v>136468</v>
+        <v>136804</v>
       </c>
       <c r="K80" t="n">
         <v>30</v>
@@ -3933,13 +3933,13 @@
         <v>100</v>
       </c>
       <c r="H81" t="n">
-        <v>64145</v>
+        <v>64316</v>
       </c>
       <c r="I81" t="n">
-        <v>68214</v>
+        <v>68397</v>
       </c>
       <c r="J81" t="n">
-        <v>132359</v>
+        <v>132713</v>
       </c>
       <c r="K81" t="n">
         <v>30</v>
@@ -3974,13 +3974,13 @@
         <v>100</v>
       </c>
       <c r="H82" t="n">
-        <v>63260</v>
+        <v>63439</v>
       </c>
       <c r="I82" t="n">
-        <v>66195</v>
+        <v>66382</v>
       </c>
       <c r="J82" t="n">
-        <v>129456</v>
+        <v>129821</v>
       </c>
       <c r="K82" t="n">
         <v>30</v>
@@ -4015,16 +4015,16 @@
         <v>100</v>
       </c>
       <c r="H83" t="n">
-        <v>62786</v>
+        <v>62971</v>
       </c>
       <c r="I83" t="n">
-        <v>64357</v>
+        <v>64546</v>
       </c>
       <c r="J83" t="n">
-        <v>127144</v>
+        <v>127518</v>
       </c>
       <c r="K83" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L83" t="n">
         <v>30</v>
@@ -4056,13 +4056,13 @@
         <v>100</v>
       </c>
       <c r="H84" t="n">
-        <v>62153</v>
+        <v>62334</v>
       </c>
       <c r="I84" t="n">
-        <v>64413</v>
+        <v>64601</v>
       </c>
       <c r="J84" t="n">
-        <v>126566</v>
+        <v>126935</v>
       </c>
       <c r="K84" t="n">
         <v>29</v>
@@ -4097,13 +4097,13 @@
         <v>100</v>
       </c>
       <c r="H85" t="n">
-        <v>61012</v>
+        <v>61189</v>
       </c>
       <c r="I85" t="n">
-        <v>64428</v>
+        <v>64614</v>
       </c>
       <c r="J85" t="n">
-        <v>125440</v>
+        <v>125803</v>
       </c>
       <c r="K85" t="n">
         <v>29</v>
@@ -4138,13 +4138,13 @@
         <v>100</v>
       </c>
       <c r="H86" t="n">
-        <v>60634</v>
+        <v>60806</v>
       </c>
       <c r="I86" t="n">
-        <v>64741</v>
+        <v>64924</v>
       </c>
       <c r="J86" t="n">
-        <v>125376</v>
+        <v>125730</v>
       </c>
       <c r="K86" t="n">
         <v>29</v>
@@ -4153,7 +4153,7 @@
         <v>31</v>
       </c>
       <c r="M86" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -4179,13 +4179,13 @@
         <v>100</v>
       </c>
       <c r="H87" t="n">
-        <v>60351</v>
+        <v>60515</v>
       </c>
       <c r="I87" t="n">
-        <v>65152</v>
+        <v>65329</v>
       </c>
       <c r="J87" t="n">
-        <v>125502</v>
+        <v>125844</v>
       </c>
       <c r="K87" t="n">
         <v>29</v>
@@ -4220,13 +4220,13 @@
         <v>100</v>
       </c>
       <c r="H88" t="n">
-        <v>59539</v>
+        <v>59694</v>
       </c>
       <c r="I88" t="n">
-        <v>64970</v>
+        <v>65139</v>
       </c>
       <c r="J88" t="n">
-        <v>124510</v>
+        <v>124833</v>
       </c>
       <c r="K88" t="n">
         <v>29</v>
@@ -4261,13 +4261,13 @@
         <v>100</v>
       </c>
       <c r="H89" t="n">
-        <v>60176</v>
+        <v>60324</v>
       </c>
       <c r="I89" t="n">
-        <v>65576</v>
+        <v>65738</v>
       </c>
       <c r="J89" t="n">
-        <v>125752</v>
+        <v>126062</v>
       </c>
       <c r="K89" t="n">
         <v>29</v>
@@ -4302,13 +4302,13 @@
         <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>59648</v>
+        <v>59786</v>
       </c>
       <c r="I90" t="n">
-        <v>66284</v>
+        <v>66438</v>
       </c>
       <c r="J90" t="n">
-        <v>125932</v>
+        <v>126223</v>
       </c>
       <c r="K90" t="n">
         <v>29</v>
@@ -4343,22 +4343,22 @@
         <v>100</v>
       </c>
       <c r="H91" t="n">
-        <v>58562</v>
+        <v>58676</v>
       </c>
       <c r="I91" t="n">
-        <v>63559</v>
+        <v>63682</v>
       </c>
       <c r="J91" t="n">
-        <v>122121</v>
+        <v>122358</v>
       </c>
       <c r="K91" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L91" t="n">
         <v>31</v>
       </c>
       <c r="M91" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
@@ -4384,13 +4384,13 @@
         <v>100</v>
       </c>
       <c r="H92" t="n">
-        <v>58426</v>
+        <v>58518</v>
       </c>
       <c r="I92" t="n">
-        <v>59738</v>
+        <v>59832</v>
       </c>
       <c r="J92" t="n">
-        <v>118164</v>
+        <v>118350</v>
       </c>
       <c r="K92" t="n">
         <v>29</v>
@@ -4425,16 +4425,16 @@
         <v>100</v>
       </c>
       <c r="H93" t="n">
-        <v>57891</v>
+        <v>57961</v>
       </c>
       <c r="I93" t="n">
-        <v>60036</v>
+        <v>60109</v>
       </c>
       <c r="J93" t="n">
-        <v>117927</v>
+        <v>118070</v>
       </c>
       <c r="K93" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L93" t="n">
         <v>30</v>
@@ -4466,19 +4466,19 @@
         <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>57220</v>
+        <v>57269</v>
       </c>
       <c r="I94" t="n">
-        <v>57615</v>
+        <v>57664</v>
       </c>
       <c r="J94" t="n">
-        <v>114834</v>
+        <v>114933</v>
       </c>
       <c r="K94" t="n">
         <v>28</v>
       </c>
       <c r="L94" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M94" t="n">
         <v>57</v>
@@ -4507,16 +4507,16 @@
         <v>100</v>
       </c>
       <c r="H95" t="n">
-        <v>57089</v>
+        <v>57126</v>
       </c>
       <c r="I95" t="n">
-        <v>57435</v>
+        <v>57472</v>
       </c>
       <c r="J95" t="n">
-        <v>114525</v>
+        <v>114598</v>
       </c>
       <c r="K95" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L95" t="n">
         <v>29</v>
@@ -4548,13 +4548,13 @@
         <v>100</v>
       </c>
       <c r="H96" t="n">
-        <v>55380</v>
+        <v>55391</v>
       </c>
       <c r="I96" t="n">
-        <v>58045</v>
+        <v>58056</v>
       </c>
       <c r="J96" t="n">
-        <v>113425</v>
+        <v>113447</v>
       </c>
       <c r="K96" t="n">
         <v>28</v>
@@ -4589,22 +4589,22 @@
         <v>100</v>
       </c>
       <c r="H97" t="n">
-        <v>54324</v>
+        <v>54317</v>
       </c>
       <c r="I97" t="n">
-        <v>58054</v>
+        <v>58046</v>
       </c>
       <c r="J97" t="n">
-        <v>112378</v>
+        <v>112363</v>
       </c>
       <c r="K97" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L97" t="n">
         <v>29</v>
       </c>
       <c r="M97" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98">
@@ -4630,13 +4630,13 @@
         <v>100</v>
       </c>
       <c r="H98" t="n">
-        <v>54760</v>
+        <v>54735</v>
       </c>
       <c r="I98" t="n">
-        <v>57870</v>
+        <v>57844</v>
       </c>
       <c r="J98" t="n">
-        <v>112630</v>
+        <v>112579</v>
       </c>
       <c r="K98" t="n">
         <v>28</v>
@@ -4671,13 +4671,13 @@
         <v>100</v>
       </c>
       <c r="H99" t="n">
-        <v>54290</v>
+        <v>54250</v>
       </c>
       <c r="I99" t="n">
-        <v>56837</v>
+        <v>56794</v>
       </c>
       <c r="J99" t="n">
-        <v>111127</v>
+        <v>111044</v>
       </c>
       <c r="K99" t="n">
         <v>28</v>
@@ -4686,7 +4686,7 @@
         <v>29</v>
       </c>
       <c r="M99" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100">
@@ -4712,13 +4712,13 @@
         <v>100</v>
       </c>
       <c r="H100" t="n">
-        <v>54521</v>
+        <v>54464</v>
       </c>
       <c r="I100" t="n">
-        <v>55905</v>
+        <v>55846</v>
       </c>
       <c r="J100" t="n">
-        <v>110425</v>
+        <v>110310</v>
       </c>
       <c r="K100" t="n">
         <v>28</v>
@@ -4727,7 +4727,7 @@
         <v>29</v>
       </c>
       <c r="M100" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101">
@@ -4753,13 +4753,13 @@
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>53629</v>
+        <v>53557</v>
       </c>
       <c r="I101" t="n">
-        <v>56160</v>
+        <v>56085</v>
       </c>
       <c r="J101" t="n">
-        <v>109788</v>
+        <v>109642</v>
       </c>
       <c r="K101" t="n">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102">
@@ -4794,13 +4794,13 @@
         <v>100</v>
       </c>
       <c r="H102" t="n">
-        <v>54164</v>
+        <v>54077</v>
       </c>
       <c r="I102" t="n">
-        <v>56061</v>
+        <v>55971</v>
       </c>
       <c r="J102" t="n">
-        <v>110226</v>
+        <v>110048</v>
       </c>
       <c r="K102" t="n">
         <v>28</v>
@@ -4835,13 +4835,13 @@
         <v>100</v>
       </c>
       <c r="H103" t="n">
-        <v>53545</v>
+        <v>53444</v>
       </c>
       <c r="I103" t="n">
-        <v>55479</v>
+        <v>55375</v>
       </c>
       <c r="J103" t="n">
-        <v>109024</v>
+        <v>108820</v>
       </c>
       <c r="K103" t="n">
         <v>28</v>
@@ -4876,13 +4876,13 @@
         <v>100</v>
       </c>
       <c r="H104" t="n">
-        <v>52986</v>
+        <v>52873</v>
       </c>
       <c r="I104" t="n">
-        <v>55704</v>
+        <v>55585</v>
       </c>
       <c r="J104" t="n">
-        <v>108690</v>
+        <v>108457</v>
       </c>
       <c r="K104" t="n">
         <v>28</v>
@@ -4917,13 +4917,13 @@
         <v>100</v>
       </c>
       <c r="H105" t="n">
-        <v>52400</v>
+        <v>52275</v>
       </c>
       <c r="I105" t="n">
-        <v>55588</v>
+        <v>55456</v>
       </c>
       <c r="J105" t="n">
-        <v>107989</v>
+        <v>107731</v>
       </c>
       <c r="K105" t="n">
         <v>28</v>
@@ -4958,13 +4958,13 @@
         <v>100</v>
       </c>
       <c r="H106" t="n">
-        <v>51567</v>
+        <v>51431</v>
       </c>
       <c r="I106" t="n">
-        <v>54628</v>
+        <v>54484</v>
       </c>
       <c r="J106" t="n">
-        <v>106195</v>
+        <v>105916</v>
       </c>
       <c r="K106" t="n">
         <v>27</v>
@@ -4973,7 +4973,7 @@
         <v>29</v>
       </c>
       <c r="M106" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107">
@@ -4999,13 +4999,13 @@
         <v>100</v>
       </c>
       <c r="H107" t="n">
-        <v>50945</v>
+        <v>50805</v>
       </c>
       <c r="I107" t="n">
-        <v>55844</v>
+        <v>55690</v>
       </c>
       <c r="J107" t="n">
-        <v>106788</v>
+        <v>106495</v>
       </c>
       <c r="K107" t="n">
         <v>27</v>
@@ -5040,13 +5040,13 @@
         <v>100</v>
       </c>
       <c r="H108" t="n">
-        <v>49076</v>
+        <v>48924</v>
       </c>
       <c r="I108" t="n">
-        <v>51919</v>
+        <v>51759</v>
       </c>
       <c r="J108" t="n">
-        <v>100995</v>
+        <v>100683</v>
       </c>
       <c r="K108" t="n">
         <v>26</v>
@@ -5055,7 +5055,7 @@
         <v>28</v>
       </c>
       <c r="M108" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109">
@@ -5081,13 +5081,13 @@
         <v>100</v>
       </c>
       <c r="H109" t="n">
-        <v>48592</v>
+        <v>48431</v>
       </c>
       <c r="I109" t="n">
-        <v>51413</v>
+        <v>51243</v>
       </c>
       <c r="J109" t="n">
-        <v>100005</v>
+        <v>99674</v>
       </c>
       <c r="K109" t="n">
         <v>26</v>
@@ -5122,13 +5122,13 @@
         <v>100</v>
       </c>
       <c r="H110" t="n">
-        <v>48873</v>
+        <v>48701</v>
       </c>
       <c r="I110" t="n">
-        <v>51698</v>
+        <v>51516</v>
       </c>
       <c r="J110" t="n">
-        <v>100571</v>
+        <v>100218</v>
       </c>
       <c r="K110" t="n">
         <v>27</v>
@@ -5163,13 +5163,13 @@
         <v>100</v>
       </c>
       <c r="H111" t="n">
-        <v>48100</v>
+        <v>47922</v>
       </c>
       <c r="I111" t="n">
-        <v>51718</v>
+        <v>51526</v>
       </c>
       <c r="J111" t="n">
-        <v>99819</v>
+        <v>99448</v>
       </c>
       <c r="K111" t="n">
         <v>26</v>
@@ -5204,22 +5204,22 @@
         <v>100</v>
       </c>
       <c r="H112" t="n">
-        <v>47858</v>
+        <v>47671</v>
       </c>
       <c r="I112" t="n">
-        <v>50883</v>
+        <v>50684</v>
       </c>
       <c r="J112" t="n">
-        <v>98741</v>
+        <v>98355</v>
       </c>
       <c r="K112" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L112" t="n">
         <v>28</v>
       </c>
       <c r="M112" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="113">
@@ -5245,13 +5245,13 @@
         <v>100</v>
       </c>
       <c r="H113" t="n">
-        <v>47145</v>
+        <v>46952</v>
       </c>
       <c r="I113" t="n">
-        <v>50982</v>
+        <v>50773</v>
       </c>
       <c r="J113" t="n">
-        <v>98127</v>
+        <v>97725</v>
       </c>
       <c r="K113" t="n">
         <v>26</v>
@@ -5260,7 +5260,7 @@
         <v>28</v>
       </c>
       <c r="M113" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114">
@@ -5286,19 +5286,19 @@
         <v>100</v>
       </c>
       <c r="H114" t="n">
-        <v>46976</v>
+        <v>46776</v>
       </c>
       <c r="I114" t="n">
-        <v>50996</v>
+        <v>50778</v>
       </c>
       <c r="J114" t="n">
-        <v>97972</v>
+        <v>97554</v>
       </c>
       <c r="K114" t="n">
         <v>26</v>
       </c>
       <c r="L114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M114" t="n">
         <v>55</v>
@@ -5327,16 +5327,16 @@
         <v>100</v>
       </c>
       <c r="H115" t="n">
-        <v>46807</v>
+        <v>46600</v>
       </c>
       <c r="I115" t="n">
-        <v>50851</v>
+        <v>50626</v>
       </c>
       <c r="J115" t="n">
-        <v>97658</v>
+        <v>97225</v>
       </c>
       <c r="K115" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L115" t="n">
         <v>29</v>
@@ -5368,13 +5368,13 @@
         <v>100</v>
       </c>
       <c r="H116" t="n">
-        <v>45434</v>
+        <v>45225</v>
       </c>
       <c r="I116" t="n">
-        <v>48583</v>
+        <v>48360</v>
       </c>
       <c r="J116" t="n">
-        <v>94017</v>
+        <v>93585</v>
       </c>
       <c r="K116" t="n">
         <v>26</v>
@@ -5383,7 +5383,7 @@
         <v>28</v>
       </c>
       <c r="M116" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
@@ -5409,13 +5409,13 @@
         <v>100</v>
       </c>
       <c r="H117" t="n">
-        <v>44069</v>
+        <v>43860</v>
       </c>
       <c r="I117" t="n">
-        <v>48240</v>
+        <v>48011</v>
       </c>
       <c r="J117" t="n">
-        <v>92309</v>
+        <v>91871</v>
       </c>
       <c r="K117" t="n">
         <v>25</v>
@@ -5450,13 +5450,13 @@
         <v>100</v>
       </c>
       <c r="H118" t="n">
-        <v>43382</v>
+        <v>43170</v>
       </c>
       <c r="I118" t="n">
-        <v>48158</v>
+        <v>47922</v>
       </c>
       <c r="J118" t="n">
-        <v>91540</v>
+        <v>91092</v>
       </c>
       <c r="K118" t="n">
         <v>25</v>
@@ -5491,13 +5491,13 @@
         <v>100</v>
       </c>
       <c r="H119" t="n">
-        <v>42503</v>
+        <v>42294</v>
       </c>
       <c r="I119" t="n">
-        <v>44545</v>
+        <v>44326</v>
       </c>
       <c r="J119" t="n">
-        <v>87049</v>
+        <v>86620</v>
       </c>
       <c r="K119" t="n">
         <v>25</v>
@@ -5506,7 +5506,7 @@
         <v>26</v>
       </c>
       <c r="M119" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120">
@@ -5532,13 +5532,13 @@
         <v>100</v>
       </c>
       <c r="H120" t="n">
-        <v>42423</v>
+        <v>42204</v>
       </c>
       <c r="I120" t="n">
-        <v>44634</v>
+        <v>44404</v>
       </c>
       <c r="J120" t="n">
-        <v>87057</v>
+        <v>86608</v>
       </c>
       <c r="K120" t="n">
         <v>25</v>
@@ -5573,22 +5573,22 @@
         <v>100</v>
       </c>
       <c r="H121" t="n">
-        <v>43336</v>
+        <v>43107</v>
       </c>
       <c r="I121" t="n">
-        <v>42563</v>
+        <v>42338</v>
       </c>
       <c r="J121" t="n">
-        <v>85899</v>
+        <v>85445</v>
       </c>
       <c r="K121" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L121" t="n">
         <v>25</v>
       </c>
       <c r="M121" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
@@ -5614,19 +5614,19 @@
         <v>100</v>
       </c>
       <c r="H122" t="n">
-        <v>43150</v>
+        <v>42917</v>
       </c>
       <c r="I122" t="n">
-        <v>41267</v>
+        <v>41044</v>
       </c>
       <c r="J122" t="n">
-        <v>84417</v>
+        <v>83962</v>
       </c>
       <c r="K122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L122" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M122" t="n">
         <v>50</v>
@@ -5655,13 +5655,13 @@
         <v>100</v>
       </c>
       <c r="H123" t="n">
-        <v>42190</v>
+        <v>41957</v>
       </c>
       <c r="I123" t="n">
-        <v>41567</v>
+        <v>41338</v>
       </c>
       <c r="J123" t="n">
-        <v>83756</v>
+        <v>83295</v>
       </c>
       <c r="K123" t="n">
         <v>25</v>
@@ -5696,13 +5696,13 @@
         <v>100</v>
       </c>
       <c r="H124" t="n">
-        <v>41879</v>
+        <v>41644</v>
       </c>
       <c r="I124" t="n">
-        <v>41754</v>
+        <v>41520</v>
       </c>
       <c r="J124" t="n">
-        <v>83634</v>
+        <v>83165</v>
       </c>
       <c r="K124" t="n">
         <v>25</v>
@@ -5737,13 +5737,13 @@
         <v>100</v>
       </c>
       <c r="H125" t="n">
-        <v>41090</v>
+        <v>40856</v>
       </c>
       <c r="I125" t="n">
-        <v>40804</v>
+        <v>40571</v>
       </c>
       <c r="J125" t="n">
-        <v>81894</v>
+        <v>81427</v>
       </c>
       <c r="K125" t="n">
         <v>25</v>
@@ -5752,7 +5752,7 @@
         <v>25</v>
       </c>
       <c r="M125" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126">
@@ -5778,13 +5778,13 @@
         <v>100</v>
       </c>
       <c r="H126" t="n">
-        <v>41008</v>
+        <v>40771</v>
       </c>
       <c r="I126" t="n">
-        <v>40760</v>
+        <v>40525</v>
       </c>
       <c r="J126" t="n">
-        <v>81769</v>
+        <v>81296</v>
       </c>
       <c r="K126" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
         <v>25</v>
       </c>
       <c r="M126" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="127">
@@ -5819,13 +5819,13 @@
         <v>100</v>
       </c>
       <c r="H127" t="n">
-        <v>41246</v>
+        <v>41004</v>
       </c>
       <c r="I127" t="n">
-        <v>40808</v>
+        <v>40569</v>
       </c>
       <c r="J127" t="n">
-        <v>82055</v>
+        <v>81574</v>
       </c>
       <c r="K127" t="n">
         <v>25</v>
@@ -5860,19 +5860,19 @@
         <v>100</v>
       </c>
       <c r="H128" t="n">
-        <v>39846</v>
+        <v>39610</v>
       </c>
       <c r="I128" t="n">
-        <v>38260</v>
+        <v>38033</v>
       </c>
       <c r="J128" t="n">
-        <v>78106</v>
+        <v>77642</v>
       </c>
       <c r="K128" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L128" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M128" t="n">
         <v>48</v>
@@ -5901,13 +5901,13 @@
         <v>100</v>
       </c>
       <c r="H129" t="n">
-        <v>38528</v>
+        <v>38297</v>
       </c>
       <c r="I129" t="n">
-        <v>38442</v>
+        <v>38211</v>
       </c>
       <c r="J129" t="n">
-        <v>76970</v>
+        <v>76508</v>
       </c>
       <c r="K129" t="n">
         <v>24</v>
@@ -5916,7 +5916,7 @@
         <v>24</v>
       </c>
       <c r="M129" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130">
@@ -5942,13 +5942,13 @@
         <v>100</v>
       </c>
       <c r="H130" t="n">
-        <v>37633</v>
+        <v>37405</v>
       </c>
       <c r="I130" t="n">
-        <v>38069</v>
+        <v>37838</v>
       </c>
       <c r="J130" t="n">
-        <v>75702</v>
+        <v>75244</v>
       </c>
       <c r="K130" t="n">
         <v>23</v>
@@ -5983,13 +5983,13 @@
         <v>100</v>
       </c>
       <c r="H131" t="n">
-        <v>36760</v>
+        <v>36538</v>
       </c>
       <c r="I131" t="n">
-        <v>37706</v>
+        <v>37479</v>
       </c>
       <c r="J131" t="n">
-        <v>74466</v>
+        <v>74016</v>
       </c>
       <c r="K131" t="n">
         <v>23</v>
@@ -5998,7 +5998,7 @@
         <v>24</v>
       </c>
       <c r="M131" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="132">
@@ -6024,13 +6024,13 @@
         <v>100</v>
       </c>
       <c r="H132" t="n">
-        <v>34943</v>
+        <v>34728</v>
       </c>
       <c r="I132" t="n">
-        <v>37972</v>
+        <v>37738</v>
       </c>
       <c r="J132" t="n">
-        <v>72915</v>
+        <v>72466</v>
       </c>
       <c r="K132" t="n">
         <v>22</v>
@@ -6065,19 +6065,19 @@
         <v>100</v>
       </c>
       <c r="H133" t="n">
-        <v>35409</v>
+        <v>35190</v>
       </c>
       <c r="I133" t="n">
-        <v>37137</v>
+        <v>36907</v>
       </c>
       <c r="J133" t="n">
-        <v>72546</v>
+        <v>72097</v>
       </c>
       <c r="K133" t="n">
+        <v>22</v>
+      </c>
+      <c r="L133" t="n">
         <v>23</v>
-      </c>
-      <c r="L133" t="n">
-        <v>24</v>
       </c>
       <c r="M133" t="n">
         <v>46</v>
@@ -6106,13 +6106,13 @@
         <v>100</v>
       </c>
       <c r="H134" t="n">
-        <v>34934</v>
+        <v>34716</v>
       </c>
       <c r="I134" t="n">
-        <v>35997</v>
+        <v>35773</v>
       </c>
       <c r="J134" t="n">
-        <v>70931</v>
+        <v>70489</v>
       </c>
       <c r="K134" t="n">
         <v>22</v>
@@ -6121,7 +6121,7 @@
         <v>23</v>
       </c>
       <c r="M134" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="135">
@@ -6147,13 +6147,13 @@
         <v>100</v>
       </c>
       <c r="H135" t="n">
-        <v>33569</v>
+        <v>33359</v>
       </c>
       <c r="I135" t="n">
-        <v>34410</v>
+        <v>34195</v>
       </c>
       <c r="J135" t="n">
-        <v>67979</v>
+        <v>67554</v>
       </c>
       <c r="K135" t="n">
         <v>22</v>
@@ -6188,13 +6188,13 @@
         <v>100</v>
       </c>
       <c r="H136" t="n">
-        <v>32108</v>
+        <v>31907</v>
       </c>
       <c r="I136" t="n">
-        <v>35854</v>
+        <v>35630</v>
       </c>
       <c r="J136" t="n">
-        <v>67963</v>
+        <v>67536</v>
       </c>
       <c r="K136" t="n">
         <v>21</v>
@@ -6229,13 +6229,13 @@
         <v>100</v>
       </c>
       <c r="H137" t="n">
-        <v>32515</v>
+        <v>32310</v>
       </c>
       <c r="I137" t="n">
-        <v>35471</v>
+        <v>35248</v>
       </c>
       <c r="J137" t="n">
-        <v>67986</v>
+        <v>67559</v>
       </c>
       <c r="K137" t="n">
         <v>21</v>
@@ -6270,13 +6270,13 @@
         <v>100</v>
       </c>
       <c r="H138" t="n">
-        <v>32937</v>
+        <v>32730</v>
       </c>
       <c r="I138" t="n">
-        <v>34204</v>
+        <v>33989</v>
       </c>
       <c r="J138" t="n">
-        <v>67142</v>
+        <v>66719</v>
       </c>
       <c r="K138" t="n">
         <v>22</v>
@@ -6285,7 +6285,7 @@
         <v>23</v>
       </c>
       <c r="M138" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139">
@@ -6311,13 +6311,13 @@
         <v>100</v>
       </c>
       <c r="H139" t="n">
-        <v>33045</v>
+        <v>32837</v>
       </c>
       <c r="I139" t="n">
-        <v>33110</v>
+        <v>32902</v>
       </c>
       <c r="J139" t="n">
-        <v>66155</v>
+        <v>65738</v>
       </c>
       <c r="K139" t="n">
         <v>22</v>
@@ -6326,7 +6326,7 @@
         <v>22</v>
       </c>
       <c r="M139" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140">
@@ -6352,13 +6352,13 @@
         <v>100</v>
       </c>
       <c r="H140" t="n">
-        <v>32814</v>
+        <v>32608</v>
       </c>
       <c r="I140" t="n">
-        <v>32193</v>
+        <v>31991</v>
       </c>
       <c r="J140" t="n">
-        <v>65007</v>
+        <v>64598</v>
       </c>
       <c r="K140" t="n">
         <v>22</v>
@@ -6393,13 +6393,13 @@
         <v>100</v>
       </c>
       <c r="H141" t="n">
-        <v>33055</v>
+        <v>32848</v>
       </c>
       <c r="I141" t="n">
-        <v>30987</v>
+        <v>30792</v>
       </c>
       <c r="J141" t="n">
-        <v>64042</v>
+        <v>63640</v>
       </c>
       <c r="K141" t="n">
         <v>23</v>
@@ -6434,16 +6434,16 @@
         <v>100</v>
       </c>
       <c r="H142" t="n">
-        <v>32691</v>
+        <v>32486</v>
       </c>
       <c r="I142" t="n">
-        <v>29906</v>
+        <v>29718</v>
       </c>
       <c r="J142" t="n">
-        <v>62596</v>
+        <v>62204</v>
       </c>
       <c r="K142" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L142" t="n">
         <v>21</v>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="H143" t="n">
-        <v>31723</v>
+        <v>31528</v>
       </c>
       <c r="I143" t="n">
-        <v>30397</v>
+        <v>30210</v>
       </c>
       <c r="J143" t="n">
-        <v>62120</v>
+        <v>61738</v>
       </c>
       <c r="K143" t="n">
         <v>22</v>
@@ -6490,7 +6490,7 @@
         <v>21</v>
       </c>
       <c r="M143" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="144">
@@ -6516,13 +6516,13 @@
         <v>100</v>
       </c>
       <c r="H144" t="n">
-        <v>31348</v>
+        <v>31153</v>
       </c>
       <c r="I144" t="n">
-        <v>27325</v>
+        <v>27155</v>
       </c>
       <c r="J144" t="n">
-        <v>58673</v>
+        <v>58309</v>
       </c>
       <c r="K144" t="n">
         <v>22</v>
@@ -6531,7 +6531,7 @@
         <v>19</v>
       </c>
       <c r="M144" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145">
@@ -6557,22 +6557,22 @@
         <v>100</v>
       </c>
       <c r="H145" t="n">
-        <v>30775</v>
+        <v>30585</v>
       </c>
       <c r="I145" t="n">
-        <v>27550</v>
+        <v>27380</v>
       </c>
       <c r="J145" t="n">
-        <v>58325</v>
+        <v>57964</v>
       </c>
       <c r="K145" t="n">
         <v>22</v>
       </c>
       <c r="L145" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M145" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="146">
@@ -6598,22 +6598,22 @@
         <v>100</v>
       </c>
       <c r="H146" t="n">
-        <v>30730</v>
+        <v>30541</v>
       </c>
       <c r="I146" t="n">
-        <v>25675</v>
+        <v>25517</v>
       </c>
       <c r="J146" t="n">
-        <v>56405</v>
+        <v>56059</v>
       </c>
       <c r="K146" t="n">
         <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M146" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147">
@@ -6639,16 +6639,16 @@
         <v>100</v>
       </c>
       <c r="H147" t="n">
-        <v>29644</v>
+        <v>29463</v>
       </c>
       <c r="I147" t="n">
-        <v>25721</v>
+        <v>25564</v>
       </c>
       <c r="J147" t="n">
-        <v>55365</v>
+        <v>55027</v>
       </c>
       <c r="K147" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L147" t="n">
         <v>19</v>
@@ -6680,13 +6680,13 @@
         <v>100</v>
       </c>
       <c r="H148" t="n">
-        <v>29841</v>
+        <v>29660</v>
       </c>
       <c r="I148" t="n">
-        <v>25746</v>
+        <v>25590</v>
       </c>
       <c r="J148" t="n">
-        <v>55587</v>
+        <v>55250</v>
       </c>
       <c r="K148" t="n">
         <v>22</v>
@@ -6695,7 +6695,7 @@
         <v>19</v>
       </c>
       <c r="M148" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149">
@@ -6721,22 +6721,22 @@
         <v>100</v>
       </c>
       <c r="H149" t="n">
-        <v>30377</v>
+        <v>30195</v>
       </c>
       <c r="I149" t="n">
-        <v>25869</v>
+        <v>25714</v>
       </c>
       <c r="J149" t="n">
-        <v>56246</v>
+        <v>55908</v>
       </c>
       <c r="K149" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L149" t="n">
         <v>19</v>
       </c>
       <c r="M149" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="150">
@@ -6762,13 +6762,13 @@
         <v>100</v>
       </c>
       <c r="H150" t="n">
-        <v>30799</v>
+        <v>30615</v>
       </c>
       <c r="I150" t="n">
-        <v>25886</v>
+        <v>25732</v>
       </c>
       <c r="J150" t="n">
-        <v>56685</v>
+        <v>56348</v>
       </c>
       <c r="K150" t="n">
         <v>23</v>
@@ -6803,13 +6803,13 @@
         <v>100</v>
       </c>
       <c r="H151" t="n">
-        <v>30568</v>
+        <v>30388</v>
       </c>
       <c r="I151" t="n">
-        <v>27097</v>
+        <v>26938</v>
       </c>
       <c r="J151" t="n">
-        <v>57666</v>
+        <v>57326</v>
       </c>
       <c r="K151" t="n">
         <v>23</v>
@@ -6844,13 +6844,13 @@
         <v>100</v>
       </c>
       <c r="H152" t="n">
-        <v>29379</v>
+        <v>29208</v>
       </c>
       <c r="I152" t="n">
-        <v>22841</v>
+        <v>22708</v>
       </c>
       <c r="J152" t="n">
-        <v>52220</v>
+        <v>51916</v>
       </c>
       <c r="K152" t="n">
         <v>22</v>
@@ -6859,7 +6859,7 @@
         <v>17</v>
       </c>
       <c r="M152" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="153">
@@ -6885,13 +6885,13 @@
         <v>100</v>
       </c>
       <c r="H153" t="n">
-        <v>29068</v>
+        <v>28901</v>
       </c>
       <c r="I153" t="n">
-        <v>22719</v>
+        <v>22588</v>
       </c>
       <c r="J153" t="n">
-        <v>51787</v>
+        <v>51490</v>
       </c>
       <c r="K153" t="n">
         <v>22</v>
@@ -6900,7 +6900,7 @@
         <v>17</v>
       </c>
       <c r="M153" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154">
@@ -6926,16 +6926,16 @@
         <v>100</v>
       </c>
       <c r="H154" t="n">
-        <v>29468</v>
+        <v>29301</v>
       </c>
       <c r="I154" t="n">
-        <v>22508</v>
+        <v>22380</v>
       </c>
       <c r="J154" t="n">
-        <v>51976</v>
+        <v>51681</v>
       </c>
       <c r="K154" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L154" t="n">
         <v>17</v>
@@ -6967,13 +6967,13 @@
         <v>100</v>
       </c>
       <c r="H155" t="n">
-        <v>29477</v>
+        <v>29315</v>
       </c>
       <c r="I155" t="n">
-        <v>22474</v>
+        <v>22350</v>
       </c>
       <c r="J155" t="n">
-        <v>51951</v>
+        <v>51666</v>
       </c>
       <c r="K155" t="n">
         <v>23</v>
@@ -7008,16 +7008,16 @@
         <v>100</v>
       </c>
       <c r="H156" t="n">
-        <v>28850</v>
+        <v>28691</v>
       </c>
       <c r="I156" t="n">
-        <v>22114</v>
+        <v>21992</v>
       </c>
       <c r="J156" t="n">
-        <v>50963</v>
+        <v>50683</v>
       </c>
       <c r="K156" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L156" t="n">
         <v>17</v>
@@ -7049,19 +7049,19 @@
         <v>100</v>
       </c>
       <c r="H157" t="n">
-        <v>28621</v>
+        <v>28466</v>
       </c>
       <c r="I157" t="n">
-        <v>22199</v>
+        <v>22079</v>
       </c>
       <c r="J157" t="n">
-        <v>50821</v>
+        <v>50545</v>
       </c>
       <c r="K157" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L157" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M157" t="n">
         <v>40</v>
@@ -7090,13 +7090,13 @@
         <v>100</v>
       </c>
       <c r="H158" t="n">
-        <v>28213</v>
+        <v>28062</v>
       </c>
       <c r="I158" t="n">
-        <v>21996</v>
+        <v>21879</v>
       </c>
       <c r="J158" t="n">
-        <v>50209</v>
+        <v>49941</v>
       </c>
       <c r="K158" t="n">
         <v>22</v>
@@ -7131,13 +7131,13 @@
         <v>100</v>
       </c>
       <c r="H159" t="n">
-        <v>28379</v>
+        <v>28230</v>
       </c>
       <c r="I159" t="n">
-        <v>21451</v>
+        <v>21339</v>
       </c>
       <c r="J159" t="n">
-        <v>49830</v>
+        <v>49569</v>
       </c>
       <c r="K159" t="n">
         <v>23</v>
@@ -7172,13 +7172,13 @@
         <v>100</v>
       </c>
       <c r="H160" t="n">
-        <v>28270</v>
+        <v>28125</v>
       </c>
       <c r="I160" t="n">
-        <v>21522</v>
+        <v>21412</v>
       </c>
       <c r="J160" t="n">
-        <v>49792</v>
+        <v>49537</v>
       </c>
       <c r="K160" t="n">
         <v>23</v>
@@ -7213,13 +7213,13 @@
         <v>100</v>
       </c>
       <c r="H161" t="n">
-        <v>27075</v>
+        <v>26938</v>
       </c>
       <c r="I161" t="n">
-        <v>21519</v>
+        <v>21411</v>
       </c>
       <c r="J161" t="n">
-        <v>48594</v>
+        <v>48349</v>
       </c>
       <c r="K161" t="n">
         <v>22</v>
@@ -7254,13 +7254,13 @@
         <v>100</v>
       </c>
       <c r="H162" t="n">
-        <v>26199</v>
+        <v>26070</v>
       </c>
       <c r="I162" t="n">
-        <v>21259</v>
+        <v>21155</v>
       </c>
       <c r="J162" t="n">
-        <v>47458</v>
+        <v>47225</v>
       </c>
       <c r="K162" t="n">
         <v>21</v>
@@ -7269,7 +7269,7 @@
         <v>17</v>
       </c>
       <c r="M162" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163">
@@ -7295,13 +7295,13 @@
         <v>100</v>
       </c>
       <c r="H163" t="n">
-        <v>25566</v>
+        <v>25443</v>
       </c>
       <c r="I163" t="n">
-        <v>19468</v>
+        <v>19374</v>
       </c>
       <c r="J163" t="n">
-        <v>45034</v>
+        <v>44818</v>
       </c>
       <c r="K163" t="n">
         <v>21</v>
@@ -7336,13 +7336,13 @@
         <v>100</v>
       </c>
       <c r="H164" t="n">
-        <v>26202</v>
+        <v>26079</v>
       </c>
       <c r="I164" t="n">
-        <v>20289</v>
+        <v>20194</v>
       </c>
       <c r="J164" t="n">
-        <v>46491</v>
+        <v>46273</v>
       </c>
       <c r="K164" t="n">
         <v>22</v>
@@ -7351,7 +7351,7 @@
         <v>17</v>
       </c>
       <c r="M164" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165">
@@ -7377,13 +7377,13 @@
         <v>100</v>
       </c>
       <c r="H165" t="n">
-        <v>26026</v>
+        <v>25906</v>
       </c>
       <c r="I165" t="n">
-        <v>19949</v>
+        <v>19857</v>
       </c>
       <c r="J165" t="n">
-        <v>45974</v>
+        <v>45764</v>
       </c>
       <c r="K165" t="n">
         <v>22</v>
@@ -7418,13 +7418,13 @@
         <v>100</v>
       </c>
       <c r="H166" t="n">
-        <v>24025</v>
+        <v>23918</v>
       </c>
       <c r="I166" t="n">
-        <v>19885</v>
+        <v>19796</v>
       </c>
       <c r="J166" t="n">
-        <v>43910</v>
+        <v>43714</v>
       </c>
       <c r="K166" t="n">
         <v>20</v>
@@ -7459,22 +7459,22 @@
         <v>100</v>
       </c>
       <c r="H167" t="n">
-        <v>23131</v>
+        <v>23033</v>
       </c>
       <c r="I167" t="n">
-        <v>20252</v>
+        <v>20166</v>
       </c>
       <c r="J167" t="n">
-        <v>43383</v>
+        <v>43198</v>
       </c>
       <c r="K167" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L167" t="n">
         <v>17</v>
       </c>
       <c r="M167" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="168">
@@ -7500,16 +7500,16 @@
         <v>100</v>
       </c>
       <c r="H168" t="n">
-        <v>24024</v>
+        <v>23923</v>
       </c>
       <c r="I168" t="n">
-        <v>20470</v>
+        <v>20384</v>
       </c>
       <c r="J168" t="n">
-        <v>44495</v>
+        <v>44307</v>
       </c>
       <c r="K168" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L168" t="n">
         <v>17</v>
@@ -7541,16 +7541,16 @@
         <v>100</v>
       </c>
       <c r="H169" t="n">
-        <v>23894</v>
+        <v>23796</v>
       </c>
       <c r="I169" t="n">
-        <v>20221</v>
+        <v>20138</v>
       </c>
       <c r="J169" t="n">
-        <v>44115</v>
+        <v>43935</v>
       </c>
       <c r="K169" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L169" t="n">
         <v>17</v>
@@ -7582,19 +7582,19 @@
         <v>100</v>
       </c>
       <c r="H170" t="n">
-        <v>23621</v>
+        <v>23528</v>
       </c>
       <c r="I170" t="n">
-        <v>20322</v>
+        <v>20242</v>
       </c>
       <c r="J170" t="n">
-        <v>43943</v>
+        <v>43769</v>
       </c>
       <c r="K170" t="n">
         <v>20</v>
       </c>
       <c r="L170" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M170" t="n">
         <v>38</v>
@@ -7623,22 +7623,22 @@
         <v>100</v>
       </c>
       <c r="H171" t="n">
-        <v>22945</v>
+        <v>22857</v>
       </c>
       <c r="I171" t="n">
-        <v>20056</v>
+        <v>19979</v>
       </c>
       <c r="J171" t="n">
-        <v>43000</v>
+        <v>42836</v>
       </c>
       <c r="K171" t="n">
         <v>20</v>
       </c>
       <c r="L171" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M171" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="172">
@@ -7664,22 +7664,22 @@
         <v>100</v>
       </c>
       <c r="H172" t="n">
-        <v>22810</v>
+        <v>22726</v>
       </c>
       <c r="I172" t="n">
-        <v>19848</v>
+        <v>19775</v>
       </c>
       <c r="J172" t="n">
-        <v>42658</v>
+        <v>42501</v>
       </c>
       <c r="K172" t="n">
         <v>20</v>
       </c>
       <c r="L172" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M172" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="173">
@@ -7705,13 +7705,13 @@
         <v>100</v>
       </c>
       <c r="H173" t="n">
-        <v>22349</v>
+        <v>22269</v>
       </c>
       <c r="I173" t="n">
-        <v>19123</v>
+        <v>19055</v>
       </c>
       <c r="J173" t="n">
-        <v>41472</v>
+        <v>41325</v>
       </c>
       <c r="K173" t="n">
         <v>20</v>
@@ -7746,13 +7746,13 @@
         <v>100</v>
       </c>
       <c r="H174" t="n">
-        <v>21650</v>
+        <v>21576</v>
       </c>
       <c r="I174" t="n">
-        <v>19049</v>
+        <v>18984</v>
       </c>
       <c r="J174" t="n">
-        <v>40699</v>
+        <v>40560</v>
       </c>
       <c r="K174" t="n">
         <v>19</v>
@@ -7761,7 +7761,7 @@
         <v>17</v>
       </c>
       <c r="M174" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175">
@@ -7787,13 +7787,13 @@
         <v>100</v>
       </c>
       <c r="H175" t="n">
-        <v>21357</v>
+        <v>21288</v>
       </c>
       <c r="I175" t="n">
-        <v>18998</v>
+        <v>18936</v>
       </c>
       <c r="J175" t="n">
-        <v>40356</v>
+        <v>40224</v>
       </c>
       <c r="K175" t="n">
         <v>19</v>
@@ -7802,7 +7802,7 @@
         <v>17</v>
       </c>
       <c r="M175" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="176">
@@ -7828,13 +7828,13 @@
         <v>100</v>
       </c>
       <c r="H176" t="n">
-        <v>22149</v>
+        <v>22080</v>
       </c>
       <c r="I176" t="n">
-        <v>17963</v>
+        <v>17907</v>
       </c>
       <c r="J176" t="n">
-        <v>40112</v>
+        <v>39986</v>
       </c>
       <c r="K176" t="n">
         <v>20</v>
@@ -7869,13 +7869,13 @@
         <v>100</v>
       </c>
       <c r="H177" t="n">
-        <v>22363</v>
+        <v>22296</v>
       </c>
       <c r="I177" t="n">
-        <v>17493</v>
+        <v>17440</v>
       </c>
       <c r="J177" t="n">
-        <v>39855</v>
+        <v>39736</v>
       </c>
       <c r="K177" t="n">
         <v>21</v>
@@ -7910,13 +7910,13 @@
         <v>100</v>
       </c>
       <c r="H178" t="n">
-        <v>22198</v>
+        <v>22136</v>
       </c>
       <c r="I178" t="n">
-        <v>16910</v>
+        <v>16862</v>
       </c>
       <c r="J178" t="n">
-        <v>39108</v>
+        <v>38997</v>
       </c>
       <c r="K178" t="n">
         <v>21</v>
@@ -7925,7 +7925,7 @@
         <v>16</v>
       </c>
       <c r="M178" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="179">
@@ -7951,13 +7951,13 @@
         <v>100</v>
       </c>
       <c r="H179" t="n">
-        <v>21972</v>
+        <v>21914</v>
       </c>
       <c r="I179" t="n">
-        <v>16606</v>
+        <v>16563</v>
       </c>
       <c r="J179" t="n">
-        <v>38578</v>
+        <v>38477</v>
       </c>
       <c r="K179" t="n">
         <v>21</v>
@@ -7966,7 +7966,7 @@
         <v>16</v>
       </c>
       <c r="M179" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="180">
@@ -7992,13 +7992,13 @@
         <v>100</v>
       </c>
       <c r="H180" t="n">
-        <v>20306</v>
+        <v>20255</v>
       </c>
       <c r="I180" t="n">
-        <v>17231</v>
+        <v>17187</v>
       </c>
       <c r="J180" t="n">
-        <v>37537</v>
+        <v>37442</v>
       </c>
       <c r="K180" t="n">
         <v>19</v>
@@ -8033,19 +8033,19 @@
         <v>100</v>
       </c>
       <c r="H181" t="n">
-        <v>20106</v>
+        <v>20058</v>
       </c>
       <c r="I181" t="n">
-        <v>17234</v>
+        <v>17193</v>
       </c>
       <c r="J181" t="n">
-        <v>37340</v>
+        <v>37251</v>
       </c>
       <c r="K181" t="n">
         <v>19</v>
       </c>
       <c r="L181" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M181" t="n">
         <v>36</v>
@@ -8074,13 +8074,13 @@
         <v>100</v>
       </c>
       <c r="H182" t="n">
-        <v>20243</v>
+        <v>20198</v>
       </c>
       <c r="I182" t="n">
-        <v>18348</v>
+        <v>18307</v>
       </c>
       <c r="J182" t="n">
-        <v>38591</v>
+        <v>38505</v>
       </c>
       <c r="K182" t="n">
         <v>20</v>
@@ -8089,7 +8089,7 @@
         <v>18</v>
       </c>
       <c r="M182" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183">
@@ -8115,13 +8115,13 @@
         <v>100</v>
       </c>
       <c r="H183" t="n">
-        <v>20044</v>
+        <v>20002</v>
       </c>
       <c r="I183" t="n">
-        <v>20434</v>
+        <v>20391</v>
       </c>
       <c r="J183" t="n">
-        <v>40478</v>
+        <v>40393</v>
       </c>
       <c r="K183" t="n">
         <v>20</v>
@@ -8130,7 +8130,7 @@
         <v>20</v>
       </c>
       <c r="M183" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184">
@@ -8156,13 +8156,13 @@
         <v>100</v>
       </c>
       <c r="H184" t="n">
-        <v>19314</v>
+        <v>19277</v>
       </c>
       <c r="I184" t="n">
-        <v>20213</v>
+        <v>20174</v>
       </c>
       <c r="J184" t="n">
-        <v>39527</v>
+        <v>39451</v>
       </c>
       <c r="K184" t="n">
         <v>19</v>
@@ -8171,7 +8171,7 @@
         <v>20</v>
       </c>
       <c r="M184" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185">
@@ -8197,22 +8197,22 @@
         <v>100</v>
       </c>
       <c r="H185" t="n">
-        <v>19667</v>
+        <v>19632</v>
       </c>
       <c r="I185" t="n">
-        <v>19456</v>
+        <v>19421</v>
       </c>
       <c r="J185" t="n">
-        <v>39123</v>
+        <v>39053</v>
       </c>
       <c r="K185" t="n">
         <v>20</v>
       </c>
       <c r="L185" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M185" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="186">
@@ -8238,13 +8238,13 @@
         <v>100</v>
       </c>
       <c r="H186" t="n">
-        <v>19825</v>
+        <v>19793</v>
       </c>
       <c r="I186" t="n">
-        <v>18881</v>
+        <v>18851</v>
       </c>
       <c r="J186" t="n">
-        <v>38707</v>
+        <v>38644</v>
       </c>
       <c r="K186" t="n">
         <v>20</v>
@@ -8253,7 +8253,7 @@
         <v>19</v>
       </c>
       <c r="M186" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="187">
@@ -8279,13 +8279,13 @@
         <v>100</v>
       </c>
       <c r="H187" t="n">
-        <v>19416</v>
+        <v>19388</v>
       </c>
       <c r="I187" t="n">
-        <v>18366</v>
+        <v>18339</v>
       </c>
       <c r="J187" t="n">
-        <v>37783</v>
+        <v>37727</v>
       </c>
       <c r="K187" t="n">
         <v>20</v>
@@ -8294,7 +8294,7 @@
         <v>19</v>
       </c>
       <c r="M187" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188">
@@ -8320,13 +8320,13 @@
         <v>100</v>
       </c>
       <c r="H188" t="n">
-        <v>19002</v>
+        <v>18977</v>
       </c>
       <c r="I188" t="n">
-        <v>17203</v>
+        <v>17180</v>
       </c>
       <c r="J188" t="n">
-        <v>36205</v>
+        <v>36157</v>
       </c>
       <c r="K188" t="n">
         <v>20</v>
@@ -8335,7 +8335,7 @@
         <v>18</v>
       </c>
       <c r="M188" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="189">
@@ -8361,22 +8361,22 @@
         <v>100</v>
       </c>
       <c r="H189" t="n">
-        <v>18752</v>
+        <v>18731</v>
       </c>
       <c r="I189" t="n">
-        <v>16642</v>
+        <v>16622</v>
       </c>
       <c r="J189" t="n">
-        <v>35394</v>
+        <v>35353</v>
       </c>
       <c r="K189" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M189" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="190">
@@ -8402,22 +8402,22 @@
         <v>100</v>
       </c>
       <c r="H190" t="n">
-        <v>19261</v>
+        <v>19241</v>
       </c>
       <c r="I190" t="n">
-        <v>16420</v>
+        <v>16404</v>
       </c>
       <c r="J190" t="n">
-        <v>35681</v>
+        <v>35645</v>
       </c>
       <c r="K190" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L190" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M190" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="191">
@@ -8443,22 +8443,22 @@
         <v>100</v>
       </c>
       <c r="H191" t="n">
-        <v>19104</v>
+        <v>19090</v>
       </c>
       <c r="I191" t="n">
-        <v>16130</v>
+        <v>16117</v>
       </c>
       <c r="J191" t="n">
-        <v>35234</v>
+        <v>35207</v>
       </c>
       <c r="K191" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L191" t="n">
         <v>17</v>
       </c>
       <c r="M191" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="192">
@@ -8484,13 +8484,13 @@
         <v>100</v>
       </c>
       <c r="H192" t="n">
-        <v>18718</v>
+        <v>18705</v>
       </c>
       <c r="I192" t="n">
-        <v>15780</v>
+        <v>15769</v>
       </c>
       <c r="J192" t="n">
-        <v>34499</v>
+        <v>34475</v>
       </c>
       <c r="K192" t="n">
         <v>20</v>
@@ -8525,13 +8525,13 @@
         <v>100</v>
       </c>
       <c r="H193" t="n">
-        <v>18495</v>
+        <v>18485</v>
       </c>
       <c r="I193" t="n">
-        <v>15406</v>
+        <v>15398</v>
       </c>
       <c r="J193" t="n">
-        <v>33901</v>
+        <v>33883</v>
       </c>
       <c r="K193" t="n">
         <v>20</v>
@@ -8566,13 +8566,13 @@
         <v>100</v>
       </c>
       <c r="H194" t="n">
-        <v>18303</v>
+        <v>18296</v>
       </c>
       <c r="I194" t="n">
-        <v>15416</v>
+        <v>15410</v>
       </c>
       <c r="J194" t="n">
-        <v>33719</v>
+        <v>33706</v>
       </c>
       <c r="K194" t="n">
         <v>20</v>
@@ -8607,13 +8607,13 @@
         <v>100</v>
       </c>
       <c r="H195" t="n">
-        <v>17941</v>
+        <v>17936</v>
       </c>
       <c r="I195" t="n">
-        <v>15414</v>
+        <v>15410</v>
       </c>
       <c r="J195" t="n">
-        <v>33354</v>
+        <v>33346</v>
       </c>
       <c r="K195" t="n">
         <v>20</v>
@@ -8622,7 +8622,7 @@
         <v>17</v>
       </c>
       <c r="M195" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="196">
@@ -8648,13 +8648,13 @@
         <v>100</v>
       </c>
       <c r="H196" t="n">
-        <v>18194</v>
+        <v>18192</v>
       </c>
       <c r="I196" t="n">
-        <v>15342</v>
+        <v>15340</v>
       </c>
       <c r="J196" t="n">
-        <v>33536</v>
+        <v>33533</v>
       </c>
       <c r="K196" t="n">
         <v>20</v>
@@ -8689,13 +8689,13 @@
         <v>100</v>
       </c>
       <c r="H197" t="n">
-        <v>18054</v>
+        <v>18055</v>
       </c>
       <c r="I197" t="n">
-        <v>14643</v>
+        <v>14644</v>
       </c>
       <c r="J197" t="n">
-        <v>32698</v>
+        <v>32700</v>
       </c>
       <c r="K197" t="n">
         <v>20</v>
@@ -8730,13 +8730,13 @@
         <v>100</v>
       </c>
       <c r="H198" t="n">
-        <v>17303</v>
+        <v>17307</v>
       </c>
       <c r="I198" t="n">
-        <v>14586</v>
+        <v>14589</v>
       </c>
       <c r="J198" t="n">
-        <v>31889</v>
+        <v>31896</v>
       </c>
       <c r="K198" t="n">
         <v>19</v>
@@ -8745,7 +8745,7 @@
         <v>16</v>
       </c>
       <c r="M198" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199">
@@ -8771,13 +8771,13 @@
         <v>100</v>
       </c>
       <c r="H199" t="n">
-        <v>17139</v>
+        <v>17145</v>
       </c>
       <c r="I199" t="n">
-        <v>14677</v>
+        <v>14683</v>
       </c>
       <c r="J199" t="n">
-        <v>31816</v>
+        <v>31827</v>
       </c>
       <c r="K199" t="n">
         <v>19</v>
@@ -8786,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="M199" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="200">
@@ -8812,13 +8812,13 @@
         <v>100</v>
       </c>
       <c r="H200" t="n">
-        <v>16909</v>
+        <v>16917</v>
       </c>
       <c r="I200" t="n">
-        <v>14093</v>
+        <v>14100</v>
       </c>
       <c r="J200" t="n">
-        <v>31002</v>
+        <v>31018</v>
       </c>
       <c r="K200" t="n">
         <v>19</v>
@@ -8827,7 +8827,7 @@
         <v>16</v>
       </c>
       <c r="M200" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="201">
@@ -8853,13 +8853,13 @@
         <v>100</v>
       </c>
       <c r="H201" t="n">
-        <v>17027</v>
+        <v>17038</v>
       </c>
       <c r="I201" t="n">
-        <v>14000</v>
+        <v>14009</v>
       </c>
       <c r="J201" t="n">
-        <v>31027</v>
+        <v>31047</v>
       </c>
       <c r="K201" t="n">
         <v>19</v>
@@ -8894,13 +8894,13 @@
         <v>100</v>
       </c>
       <c r="H202" t="n">
-        <v>16679</v>
+        <v>16692</v>
       </c>
       <c r="I202" t="n">
-        <v>14044</v>
+        <v>14055</v>
       </c>
       <c r="J202" t="n">
-        <v>30723</v>
+        <v>30747</v>
       </c>
       <c r="K202" t="n">
         <v>19</v>
@@ -8935,13 +8935,13 @@
         <v>100</v>
       </c>
       <c r="H203" t="n">
-        <v>15881</v>
+        <v>15897</v>
       </c>
       <c r="I203" t="n">
-        <v>13734</v>
+        <v>13748</v>
       </c>
       <c r="J203" t="n">
-        <v>29615</v>
+        <v>29645</v>
       </c>
       <c r="K203" t="n">
         <v>18</v>
@@ -8976,13 +8976,13 @@
         <v>100</v>
       </c>
       <c r="H204" t="n">
-        <v>15210</v>
+        <v>15226</v>
       </c>
       <c r="I204" t="n">
-        <v>13765</v>
+        <v>13779</v>
       </c>
       <c r="J204" t="n">
-        <v>28974</v>
+        <v>29005</v>
       </c>
       <c r="K204" t="n">
         <v>18</v>
@@ -9017,13 +9017,13 @@
         <v>100</v>
       </c>
       <c r="H205" t="n">
-        <v>15454</v>
+        <v>15472</v>
       </c>
       <c r="I205" t="n">
-        <v>15454</v>
+        <v>15472</v>
       </c>
       <c r="J205" t="n">
-        <v>30907</v>
+        <v>30944</v>
       </c>
       <c r="K205" t="n">
         <v>18</v>
@@ -9032,7 +9032,7 @@
         <v>18</v>
       </c>
       <c r="M205" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="206">
@@ -9058,13 +9058,13 @@
         <v>100</v>
       </c>
       <c r="H206" t="n">
-        <v>14797</v>
+        <v>14817</v>
       </c>
       <c r="I206" t="n">
-        <v>13701</v>
+        <v>13719</v>
       </c>
       <c r="J206" t="n">
-        <v>28498</v>
+        <v>28536</v>
       </c>
       <c r="K206" t="n">
         <v>18</v>
@@ -9073,7 +9073,7 @@
         <v>17</v>
       </c>
       <c r="M206" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="207">
@@ -9099,13 +9099,13 @@
         <v>100</v>
       </c>
       <c r="H207" t="n">
-        <v>14934</v>
+        <v>14956</v>
       </c>
       <c r="I207" t="n">
-        <v>13796</v>
+        <v>13816</v>
       </c>
       <c r="J207" t="n">
-        <v>28730</v>
+        <v>28772</v>
       </c>
       <c r="K207" t="n">
         <v>19</v>
@@ -9140,13 +9140,13 @@
         <v>100</v>
       </c>
       <c r="H208" t="n">
-        <v>14526</v>
+        <v>14549</v>
       </c>
       <c r="I208" t="n">
-        <v>13850</v>
+        <v>13871</v>
       </c>
       <c r="J208" t="n">
-        <v>28375</v>
+        <v>28420</v>
       </c>
       <c r="K208" t="n">
         <v>19</v>
@@ -9181,13 +9181,13 @@
         <v>100</v>
       </c>
       <c r="H209" t="n">
-        <v>14461</v>
+        <v>14486</v>
       </c>
       <c r="I209" t="n">
-        <v>14009</v>
+        <v>14033</v>
       </c>
       <c r="J209" t="n">
-        <v>28471</v>
+        <v>28519</v>
       </c>
       <c r="K209" t="n">
         <v>19</v>
@@ -9222,16 +9222,16 @@
         <v>100</v>
       </c>
       <c r="H210" t="n">
-        <v>14044</v>
+        <v>14069</v>
       </c>
       <c r="I210" t="n">
-        <v>14090</v>
+        <v>14115</v>
       </c>
       <c r="J210" t="n">
-        <v>28133</v>
+        <v>28184</v>
       </c>
       <c r="K210" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L210" t="n">
         <v>20</v>
@@ -9263,22 +9263,22 @@
         <v>100</v>
       </c>
       <c r="H211" t="n">
-        <v>13749</v>
+        <v>13782</v>
       </c>
       <c r="I211" t="n">
-        <v>14195</v>
+        <v>14229</v>
       </c>
       <c r="J211" t="n">
-        <v>27944</v>
+        <v>28011</v>
       </c>
       <c r="K211" t="n">
         <v>20</v>
       </c>
       <c r="L211" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M211" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="212">
@@ -9304,22 +9304,22 @@
         <v>100</v>
       </c>
       <c r="H212" t="n">
-        <v>13001</v>
+        <v>13039</v>
       </c>
       <c r="I212" t="n">
-        <v>13763</v>
+        <v>13804</v>
       </c>
       <c r="J212" t="n">
-        <v>26764</v>
+        <v>26843</v>
       </c>
       <c r="K212" t="n">
+        <v>19</v>
+      </c>
+      <c r="L212" t="n">
         <v>20</v>
       </c>
-      <c r="L212" t="n">
-        <v>21</v>
-      </c>
       <c r="M212" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="213">
@@ -9345,22 +9345,22 @@
         <v>100</v>
       </c>
       <c r="H213" t="n">
-        <v>13243</v>
+        <v>13289</v>
       </c>
       <c r="I213" t="n">
-        <v>13630</v>
+        <v>13678</v>
       </c>
       <c r="J213" t="n">
-        <v>26873</v>
+        <v>26967</v>
       </c>
       <c r="K213" t="n">
+        <v>20</v>
+      </c>
+      <c r="L213" t="n">
         <v>21</v>
       </c>
-      <c r="L213" t="n">
-        <v>22</v>
-      </c>
       <c r="M213" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214">
@@ -9386,22 +9386,22 @@
         <v>100</v>
       </c>
       <c r="H214" t="n">
-        <v>12662</v>
+        <v>12713</v>
       </c>
       <c r="I214" t="n">
-        <v>13699</v>
+        <v>13754</v>
       </c>
       <c r="J214" t="n">
-        <v>26361</v>
+        <v>26467</v>
       </c>
       <c r="K214" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L214" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M214" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215">
@@ -9427,22 +9427,22 @@
         <v>100</v>
       </c>
       <c r="H215" t="n">
-        <v>12795</v>
+        <v>12855</v>
       </c>
       <c r="I215" t="n">
-        <v>13750</v>
+        <v>13814</v>
       </c>
       <c r="J215" t="n">
-        <v>26545</v>
+        <v>26669</v>
       </c>
       <c r="K215" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L215" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M215" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="216">
@@ -9468,22 +9468,22 @@
         <v>100</v>
       </c>
       <c r="H216" t="n">
-        <v>12160</v>
+        <v>12223</v>
       </c>
       <c r="I216" t="n">
-        <v>13719</v>
+        <v>13789</v>
       </c>
       <c r="J216" t="n">
-        <v>25879</v>
+        <v>26012</v>
       </c>
       <c r="K216" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L216" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M216" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="217">
@@ -9509,13 +9509,13 @@
         <v>100</v>
       </c>
       <c r="H217" t="n">
-        <v>12236</v>
+        <v>12305</v>
       </c>
       <c r="I217" t="n">
-        <v>13856</v>
+        <v>13935</v>
       </c>
       <c r="J217" t="n">
-        <v>26092</v>
+        <v>26240</v>
       </c>
       <c r="K217" t="n">
         <v>22</v>
@@ -9524,7 +9524,7 @@
         <v>25</v>
       </c>
       <c r="M217" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="218">
@@ -9550,22 +9550,22 @@
         <v>100</v>
       </c>
       <c r="H218" t="n">
-        <v>12128</v>
+        <v>12203</v>
       </c>
       <c r="I218" t="n">
-        <v>12097</v>
+        <v>12172</v>
       </c>
       <c r="J218" t="n">
-        <v>24226</v>
+        <v>24376</v>
       </c>
       <c r="K218" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L218" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M218" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="219">
@@ -9591,22 +9591,22 @@
         <v>100</v>
       </c>
       <c r="H219" t="n">
-        <v>12239</v>
+        <v>12322</v>
       </c>
       <c r="I219" t="n">
-        <v>11696</v>
+        <v>11774</v>
       </c>
       <c r="J219" t="n">
-        <v>23935</v>
+        <v>24096</v>
       </c>
       <c r="K219" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L219" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M219" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="220">
@@ -9632,22 +9632,22 @@
         <v>100</v>
       </c>
       <c r="H220" t="n">
-        <v>12118</v>
+        <v>12206</v>
       </c>
       <c r="I220" t="n">
-        <v>11676</v>
+        <v>11761</v>
       </c>
       <c r="J220" t="n">
-        <v>23794</v>
+        <v>23966</v>
       </c>
       <c r="K220" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L220" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M220" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="221">
@@ -9673,22 +9673,22 @@
         <v>100</v>
       </c>
       <c r="H221" t="n">
-        <v>11712</v>
+        <v>11803</v>
       </c>
       <c r="I221" t="n">
-        <v>11717</v>
+        <v>11808</v>
       </c>
       <c r="J221" t="n">
-        <v>23429</v>
+        <v>23611</v>
       </c>
       <c r="K221" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L221" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M221" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222">
@@ -9714,22 +9714,22 @@
         <v>100</v>
       </c>
       <c r="H222" t="n">
-        <v>11590</v>
+        <v>11686</v>
       </c>
       <c r="I222" t="n">
-        <v>11716</v>
+        <v>11813</v>
       </c>
       <c r="J222" t="n">
-        <v>23305</v>
+        <v>23499</v>
       </c>
       <c r="K222" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L222" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M222" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223">
@@ -9755,22 +9755,22 @@
         <v>100</v>
       </c>
       <c r="H223" t="n">
-        <v>11678</v>
+        <v>11781</v>
       </c>
       <c r="I223" t="n">
-        <v>11932</v>
+        <v>12037</v>
       </c>
       <c r="J223" t="n">
-        <v>23610</v>
+        <v>23818</v>
       </c>
       <c r="K223" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L223" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M223" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="224">
@@ -9796,22 +9796,22 @@
         <v>100</v>
       </c>
       <c r="H224" t="n">
-        <v>12028</v>
+        <v>12140</v>
       </c>
       <c r="I224" t="n">
-        <v>11674</v>
+        <v>11782</v>
       </c>
       <c r="J224" t="n">
-        <v>23702</v>
+        <v>23922</v>
       </c>
       <c r="K224" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L224" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M224" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="225">
@@ -9837,22 +9837,22 @@
         <v>100</v>
       </c>
       <c r="H225" t="n">
-        <v>11920</v>
+        <v>12037</v>
       </c>
       <c r="I225" t="n">
-        <v>11596</v>
+        <v>11710</v>
       </c>
       <c r="J225" t="n">
-        <v>23516</v>
+        <v>23747</v>
       </c>
       <c r="K225" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L225" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M225" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="226">
@@ -9878,22 +9878,22 @@
         <v>100</v>
       </c>
       <c r="H226" t="n">
-        <v>12129</v>
+        <v>12254</v>
       </c>
       <c r="I226" t="n">
-        <v>11593</v>
+        <v>11713</v>
       </c>
       <c r="J226" t="n">
-        <v>23723</v>
+        <v>23967</v>
       </c>
       <c r="K226" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L226" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M226" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="227">
@@ -9919,22 +9919,22 @@
         <v>100</v>
       </c>
       <c r="H227" t="n">
-        <v>11875</v>
+        <v>12004</v>
       </c>
       <c r="I227" t="n">
-        <v>11639</v>
+        <v>11766</v>
       </c>
       <c r="J227" t="n">
-        <v>23514</v>
+        <v>23770</v>
       </c>
       <c r="K227" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L227" t="n">
         <v>23</v>
       </c>
       <c r="M227" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="228">
@@ -9960,22 +9960,22 @@
         <v>100</v>
       </c>
       <c r="H228" t="n">
-        <v>11832</v>
+        <v>11965</v>
       </c>
       <c r="I228" t="n">
-        <v>11614</v>
+        <v>11745</v>
       </c>
       <c r="J228" t="n">
-        <v>23445</v>
+        <v>23710</v>
       </c>
       <c r="K228" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L228" t="n">
         <v>23</v>
       </c>
       <c r="M228" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="229">
@@ -10001,13 +10001,13 @@
         <v>100</v>
       </c>
       <c r="H229" t="n">
-        <v>12016</v>
+        <v>12157</v>
       </c>
       <c r="I229" t="n">
-        <v>11161</v>
+        <v>11293</v>
       </c>
       <c r="J229" t="n">
-        <v>23177</v>
+        <v>23450</v>
       </c>
       <c r="K229" t="n">
         <v>24</v>
@@ -10042,13 +10042,13 @@
         <v>100</v>
       </c>
       <c r="H230" t="n">
-        <v>11709</v>
+        <v>11852</v>
       </c>
       <c r="I230" t="n">
-        <v>11659</v>
+        <v>11802</v>
       </c>
       <c r="J230" t="n">
-        <v>23368</v>
+        <v>23654</v>
       </c>
       <c r="K230" t="n">
         <v>23</v>
@@ -10083,13 +10083,13 @@
         <v>100</v>
       </c>
       <c r="H231" t="n">
-        <v>11523</v>
+        <v>11669</v>
       </c>
       <c r="I231" t="n">
-        <v>11557</v>
+        <v>11704</v>
       </c>
       <c r="J231" t="n">
-        <v>23080</v>
+        <v>23373</v>
       </c>
       <c r="K231" t="n">
         <v>23</v>
@@ -10124,13 +10124,13 @@
         <v>100</v>
       </c>
       <c r="H232" t="n">
-        <v>11775</v>
+        <v>11930</v>
       </c>
       <c r="I232" t="n">
-        <v>11274</v>
+        <v>11423</v>
       </c>
       <c r="J232" t="n">
-        <v>23049</v>
+        <v>23353</v>
       </c>
       <c r="K232" t="n">
         <v>24</v>
@@ -10165,13 +10165,13 @@
         <v>100</v>
       </c>
       <c r="H233" t="n">
-        <v>11496</v>
+        <v>11653</v>
       </c>
       <c r="I233" t="n">
-        <v>11307</v>
+        <v>11461</v>
       </c>
       <c r="J233" t="n">
-        <v>22803</v>
+        <v>23114</v>
       </c>
       <c r="K233" t="n">
         <v>24</v>
@@ -10206,19 +10206,19 @@
         <v>100</v>
       </c>
       <c r="H234" t="n">
-        <v>11361</v>
+        <v>11521</v>
       </c>
       <c r="I234" t="n">
-        <v>11369</v>
+        <v>11529</v>
       </c>
       <c r="J234" t="n">
-        <v>22729</v>
+        <v>23050</v>
       </c>
       <c r="K234" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L234" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M234" t="n">
         <v>47</v>
@@ -10247,13 +10247,13 @@
         <v>100</v>
       </c>
       <c r="H235" t="n">
-        <v>11229</v>
+        <v>11392</v>
       </c>
       <c r="I235" t="n">
-        <v>11004</v>
+        <v>11163</v>
       </c>
       <c r="J235" t="n">
-        <v>22233</v>
+        <v>22556</v>
       </c>
       <c r="K235" t="n">
         <v>23</v>
@@ -10288,13 +10288,13 @@
         <v>100</v>
       </c>
       <c r="H236" t="n">
-        <v>10865</v>
+        <v>11027</v>
       </c>
       <c r="I236" t="n">
-        <v>11669</v>
+        <v>11844</v>
       </c>
       <c r="J236" t="n">
-        <v>22534</v>
+        <v>22872</v>
       </c>
       <c r="K236" t="n">
         <v>23</v>
@@ -10329,13 +10329,13 @@
         <v>100</v>
       </c>
       <c r="H237" t="n">
-        <v>10877</v>
+        <v>11045</v>
       </c>
       <c r="I237" t="n">
-        <v>11707</v>
+        <v>11887</v>
       </c>
       <c r="J237" t="n">
-        <v>22584</v>
+        <v>22932</v>
       </c>
       <c r="K237" t="n">
         <v>23</v>
@@ -10370,19 +10370,19 @@
         <v>100</v>
       </c>
       <c r="H238" t="n">
-        <v>10781</v>
+        <v>10952</v>
       </c>
       <c r="I238" t="n">
-        <v>11417</v>
+        <v>11598</v>
       </c>
       <c r="J238" t="n">
-        <v>22198</v>
+        <v>22550</v>
       </c>
       <c r="K238" t="n">
         <v>23</v>
       </c>
       <c r="L238" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M238" t="n">
         <v>48</v>
@@ -10411,13 +10411,13 @@
         <v>100</v>
       </c>
       <c r="H239" t="n">
-        <v>10789</v>
+        <v>10965</v>
       </c>
       <c r="I239" t="n">
-        <v>11647</v>
+        <v>11837</v>
       </c>
       <c r="J239" t="n">
-        <v>22436</v>
+        <v>22802</v>
       </c>
       <c r="K239" t="n">
         <v>23</v>
@@ -10426,7 +10426,7 @@
         <v>25</v>
       </c>
       <c r="M239" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="240">
@@ -10452,19 +10452,19 @@
         <v>100</v>
       </c>
       <c r="H240" t="n">
-        <v>10595</v>
+        <v>10772</v>
       </c>
       <c r="I240" t="n">
-        <v>11698</v>
+        <v>11893</v>
       </c>
       <c r="J240" t="n">
-        <v>22293</v>
+        <v>22665</v>
       </c>
       <c r="K240" t="n">
         <v>23</v>
       </c>
       <c r="L240" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M240" t="n">
         <v>49</v>
@@ -10493,13 +10493,13 @@
         <v>100</v>
       </c>
       <c r="H241" t="n">
-        <v>10813</v>
+        <v>10997</v>
       </c>
       <c r="I241" t="n">
-        <v>11448</v>
+        <v>11643</v>
       </c>
       <c r="J241" t="n">
-        <v>22261</v>
+        <v>22640</v>
       </c>
       <c r="K241" t="n">
         <v>24</v>
@@ -10534,22 +10534,22 @@
         <v>100</v>
       </c>
       <c r="H242" t="n">
-        <v>10719</v>
+        <v>10907</v>
       </c>
       <c r="I242" t="n">
-        <v>11954</v>
+        <v>12163</v>
       </c>
       <c r="J242" t="n">
-        <v>22674</v>
+        <v>23070</v>
       </c>
       <c r="K242" t="n">
         <v>24</v>
       </c>
       <c r="L242" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M242" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="243">
@@ -10575,13 +10575,13 @@
         <v>100</v>
       </c>
       <c r="H243" t="n">
-        <v>10585</v>
+        <v>10774</v>
       </c>
       <c r="I243" t="n">
-        <v>11964</v>
+        <v>12177</v>
       </c>
       <c r="J243" t="n">
-        <v>22549</v>
+        <v>22952</v>
       </c>
       <c r="K243" t="n">
         <v>24</v>
@@ -10590,7 +10590,7 @@
         <v>27</v>
       </c>
       <c r="M243" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244">
@@ -10616,13 +10616,13 @@
         <v>100</v>
       </c>
       <c r="H244" t="n">
-        <v>10496</v>
+        <v>10687</v>
       </c>
       <c r="I244" t="n">
-        <v>11938</v>
+        <v>12155</v>
       </c>
       <c r="J244" t="n">
-        <v>22433</v>
+        <v>22842</v>
       </c>
       <c r="K244" t="n">
         <v>24</v>
@@ -10657,13 +10657,13 @@
         <v>100</v>
       </c>
       <c r="H245" t="n">
-        <v>10414</v>
+        <v>10608</v>
       </c>
       <c r="I245" t="n">
-        <v>12201</v>
+        <v>12428</v>
       </c>
       <c r="J245" t="n">
-        <v>22615</v>
+        <v>23036</v>
       </c>
       <c r="K245" t="n">
         <v>24</v>
@@ -10698,22 +10698,22 @@
         <v>100</v>
       </c>
       <c r="H246" t="n">
-        <v>10346</v>
+        <v>10543</v>
       </c>
       <c r="I246" t="n">
-        <v>12213</v>
+        <v>12445</v>
       </c>
       <c r="J246" t="n">
-        <v>22560</v>
+        <v>22988</v>
       </c>
       <c r="K246" t="n">
         <v>24</v>
       </c>
       <c r="L246" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M246" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247">
@@ -10739,22 +10739,22 @@
         <v>100</v>
       </c>
       <c r="H247" t="n">
-        <v>10169</v>
+        <v>10365</v>
       </c>
       <c r="I247" t="n">
-        <v>12254</v>
+        <v>12491</v>
       </c>
       <c r="J247" t="n">
-        <v>22423</v>
+        <v>22856</v>
       </c>
       <c r="K247" t="n">
         <v>24</v>
       </c>
       <c r="L247" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M247" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="248">
@@ -10780,22 +10780,22 @@
         <v>100</v>
       </c>
       <c r="H248" t="n">
-        <v>9951</v>
+        <v>10147</v>
       </c>
       <c r="I248" t="n">
-        <v>11575</v>
+        <v>11802</v>
       </c>
       <c r="J248" t="n">
-        <v>21526</v>
+        <v>21950</v>
       </c>
       <c r="K248" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L248" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M248" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="249">
@@ -10821,22 +10821,22 @@
         <v>100</v>
       </c>
       <c r="H249" t="n">
-        <v>9936</v>
+        <v>10135</v>
       </c>
       <c r="I249" t="n">
-        <v>11599</v>
+        <v>11832</v>
       </c>
       <c r="J249" t="n">
-        <v>21535</v>
+        <v>21966</v>
       </c>
       <c r="K249" t="n">
         <v>24</v>
       </c>
       <c r="L249" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M249" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="250">
@@ -10862,13 +10862,13 @@
         <v>100</v>
       </c>
       <c r="H250" t="n">
-        <v>9894</v>
+        <v>10096</v>
       </c>
       <c r="I250" t="n">
-        <v>11637</v>
+        <v>11874</v>
       </c>
       <c r="J250" t="n">
-        <v>21531</v>
+        <v>21970</v>
       </c>
       <c r="K250" t="n">
         <v>24</v>
@@ -10877,7 +10877,7 @@
         <v>28</v>
       </c>
       <c r="M250" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="251">
@@ -10903,22 +10903,22 @@
         <v>100</v>
       </c>
       <c r="H251" t="n">
-        <v>9700</v>
+        <v>9902</v>
       </c>
       <c r="I251" t="n">
-        <v>11663</v>
+        <v>11906</v>
       </c>
       <c r="J251" t="n">
-        <v>21364</v>
+        <v>21808</v>
       </c>
       <c r="K251" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L251" t="n">
         <v>28</v>
       </c>
       <c r="M251" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="252">
@@ -10944,19 +10944,19 @@
         <v>100</v>
       </c>
       <c r="H252" t="n">
-        <v>9588</v>
+        <v>9789</v>
       </c>
       <c r="I252" t="n">
-        <v>11700</v>
+        <v>11946</v>
       </c>
       <c r="J252" t="n">
-        <v>21288</v>
+        <v>21735</v>
       </c>
       <c r="K252" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L252" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M252" t="n">
         <v>52</v>
@@ -10985,13 +10985,13 @@
         <v>100</v>
       </c>
       <c r="H253" t="n">
-        <v>9638</v>
+        <v>9843</v>
       </c>
       <c r="I253" t="n">
-        <v>11755</v>
+        <v>12006</v>
       </c>
       <c r="J253" t="n">
-        <v>21393</v>
+        <v>21849</v>
       </c>
       <c r="K253" t="n">
         <v>24</v>
@@ -11026,13 +11026,13 @@
         <v>100</v>
       </c>
       <c r="H254" t="n">
-        <v>9615</v>
+        <v>9822</v>
       </c>
       <c r="I254" t="n">
-        <v>12048</v>
+        <v>12308</v>
       </c>
       <c r="J254" t="n">
-        <v>21662</v>
+        <v>22131</v>
       </c>
       <c r="K254" t="n">
         <v>24</v>
@@ -11067,13 +11067,13 @@
         <v>100</v>
       </c>
       <c r="H255" t="n">
-        <v>9612</v>
+        <v>9823</v>
       </c>
       <c r="I255" t="n">
-        <v>12088</v>
+        <v>12353</v>
       </c>
       <c r="J255" t="n">
-        <v>21700</v>
+        <v>22176</v>
       </c>
       <c r="K255" t="n">
         <v>24</v>
@@ -11082,7 +11082,7 @@
         <v>30</v>
       </c>
       <c r="M255" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="256">
@@ -11108,22 +11108,22 @@
         <v>100</v>
       </c>
       <c r="H256" t="n">
-        <v>9519</v>
+        <v>9730</v>
       </c>
       <c r="I256" t="n">
-        <v>12126</v>
+        <v>12395</v>
       </c>
       <c r="J256" t="n">
-        <v>21645</v>
+        <v>22125</v>
       </c>
       <c r="K256" t="n">
         <v>24</v>
       </c>
       <c r="L256" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M256" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="257">
@@ -11149,13 +11149,13 @@
         <v>100</v>
       </c>
       <c r="H257" t="n">
-        <v>9440</v>
+        <v>9652</v>
       </c>
       <c r="I257" t="n">
-        <v>12616</v>
+        <v>12899</v>
       </c>
       <c r="J257" t="n">
-        <v>22056</v>
+        <v>22551</v>
       </c>
       <c r="K257" t="n">
         <v>24</v>
@@ -11190,13 +11190,13 @@
         <v>100</v>
       </c>
       <c r="H258" t="n">
-        <v>9421</v>
+        <v>9635</v>
       </c>
       <c r="I258" t="n">
-        <v>12659</v>
+        <v>12946</v>
       </c>
       <c r="J258" t="n">
-        <v>22079</v>
+        <v>22581</v>
       </c>
       <c r="K258" t="n">
         <v>24</v>
@@ -11205,7 +11205,7 @@
         <v>32</v>
       </c>
       <c r="M258" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="259">
@@ -11231,19 +11231,19 @@
         <v>100</v>
       </c>
       <c r="H259" t="n">
-        <v>9194</v>
+        <v>9406</v>
       </c>
       <c r="I259" t="n">
-        <v>12644</v>
+        <v>12935</v>
       </c>
       <c r="J259" t="n">
-        <v>21839</v>
+        <v>22340</v>
       </c>
       <c r="K259" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L259" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M259" t="n">
         <v>56</v>
@@ -11272,13 +11272,13 @@
         <v>100</v>
       </c>
       <c r="H260" t="n">
-        <v>8905</v>
+        <v>9111</v>
       </c>
       <c r="I260" t="n">
-        <v>12365</v>
+        <v>12652</v>
       </c>
       <c r="J260" t="n">
-        <v>21269</v>
+        <v>21763</v>
       </c>
       <c r="K260" t="n">
         <v>23</v>
@@ -11313,13 +11313,13 @@
         <v>100</v>
       </c>
       <c r="H261" t="n">
-        <v>8988</v>
+        <v>9199</v>
       </c>
       <c r="I261" t="n">
-        <v>12417</v>
+        <v>12708</v>
       </c>
       <c r="J261" t="n">
-        <v>21405</v>
+        <v>21907</v>
       </c>
       <c r="K261" t="n">
         <v>23</v>
@@ -11328,7 +11328,7 @@
         <v>32</v>
       </c>
       <c r="M261" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="262">
@@ -11354,22 +11354,22 @@
         <v>100</v>
       </c>
       <c r="H262" t="n">
-        <v>8690</v>
+        <v>8895</v>
       </c>
       <c r="I262" t="n">
-        <v>12459</v>
+        <v>12754</v>
       </c>
       <c r="J262" t="n">
-        <v>21148</v>
+        <v>21649</v>
       </c>
       <c r="K262" t="n">
         <v>23</v>
       </c>
       <c r="L262" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M262" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263">
@@ -11395,19 +11395,19 @@
         <v>100</v>
       </c>
       <c r="H263" t="n">
-        <v>8587</v>
+        <v>8793</v>
       </c>
       <c r="I263" t="n">
-        <v>13092</v>
+        <v>13406</v>
       </c>
       <c r="J263" t="n">
-        <v>21679</v>
+        <v>22199</v>
       </c>
       <c r="K263" t="n">
         <v>23</v>
       </c>
       <c r="L263" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M263" t="n">
         <v>57</v>
@@ -11436,13 +11436,13 @@
         <v>100</v>
       </c>
       <c r="H264" t="n">
-        <v>8577</v>
+        <v>8784</v>
       </c>
       <c r="I264" t="n">
-        <v>13143</v>
+        <v>13459</v>
       </c>
       <c r="J264" t="n">
-        <v>21720</v>
+        <v>22243</v>
       </c>
       <c r="K264" t="n">
         <v>23</v>
@@ -11451,7 +11451,7 @@
         <v>35</v>
       </c>
       <c r="M264" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="265">
@@ -11477,13 +11477,13 @@
         <v>100</v>
       </c>
       <c r="H265" t="n">
-        <v>8719</v>
+        <v>8930</v>
       </c>
       <c r="I265" t="n">
-        <v>12987</v>
+        <v>13303</v>
       </c>
       <c r="J265" t="n">
-        <v>21706</v>
+        <v>22233</v>
       </c>
       <c r="K265" t="n">
         <v>23</v>
@@ -11518,13 +11518,13 @@
         <v>100</v>
       </c>
       <c r="H266" t="n">
-        <v>8950</v>
+        <v>9169</v>
       </c>
       <c r="I266" t="n">
-        <v>13450</v>
+        <v>13779</v>
       </c>
       <c r="J266" t="n">
-        <v>22400</v>
+        <v>22947</v>
       </c>
       <c r="K266" t="n">
         <v>24</v>
@@ -11533,7 +11533,7 @@
         <v>36</v>
       </c>
       <c r="M266" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="267">
@@ -11559,19 +11559,19 @@
         <v>100</v>
       </c>
       <c r="H267" t="n">
-        <v>8940</v>
+        <v>9160</v>
       </c>
       <c r="I267" t="n">
-        <v>13476</v>
+        <v>13808</v>
       </c>
       <c r="J267" t="n">
-        <v>22416</v>
+        <v>22968</v>
       </c>
       <c r="K267" t="n">
         <v>24</v>
       </c>
       <c r="L267" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M267" t="n">
         <v>61</v>
@@ -11600,13 +11600,13 @@
         <v>100</v>
       </c>
       <c r="H268" t="n">
-        <v>8907</v>
+        <v>9127</v>
       </c>
       <c r="I268" t="n">
-        <v>13503</v>
+        <v>13837</v>
       </c>
       <c r="J268" t="n">
-        <v>22410</v>
+        <v>22965</v>
       </c>
       <c r="K268" t="n">
         <v>24</v>
@@ -11641,19 +11641,19 @@
         <v>100</v>
       </c>
       <c r="H269" t="n">
-        <v>8984</v>
+        <v>9208</v>
       </c>
       <c r="I269" t="n">
-        <v>13236</v>
+        <v>13566</v>
       </c>
       <c r="J269" t="n">
-        <v>22221</v>
+        <v>22774</v>
       </c>
       <c r="K269" t="n">
         <v>25</v>
       </c>
       <c r="L269" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M269" t="n">
         <v>61</v>
@@ -11682,13 +11682,13 @@
         <v>100</v>
       </c>
       <c r="H270" t="n">
-        <v>9058</v>
+        <v>9284</v>
       </c>
       <c r="I270" t="n">
-        <v>13271</v>
+        <v>13603</v>
       </c>
       <c r="J270" t="n">
-        <v>22328</v>
+        <v>22887</v>
       </c>
       <c r="K270" t="n">
         <v>25</v>
@@ -11723,22 +11723,22 @@
         <v>100</v>
       </c>
       <c r="H271" t="n">
-        <v>9161</v>
+        <v>9391</v>
       </c>
       <c r="I271" t="n">
-        <v>13257</v>
+        <v>13591</v>
       </c>
       <c r="J271" t="n">
-        <v>22419</v>
+        <v>22982</v>
       </c>
       <c r="K271" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L271" t="n">
         <v>37</v>
       </c>
       <c r="M271" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="272">
@@ -11764,19 +11764,19 @@
         <v>100</v>
       </c>
       <c r="H272" t="n">
-        <v>8976</v>
+        <v>9202</v>
       </c>
       <c r="I272" t="n">
-        <v>12250</v>
+        <v>12559</v>
       </c>
       <c r="J272" t="n">
-        <v>21225</v>
+        <v>21761</v>
       </c>
       <c r="K272" t="n">
         <v>25</v>
       </c>
       <c r="L272" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M272" t="n">
         <v>60</v>
@@ -11805,13 +11805,13 @@
         <v>100</v>
       </c>
       <c r="H273" t="n">
-        <v>9051</v>
+        <v>9281</v>
       </c>
       <c r="I273" t="n">
-        <v>12320</v>
+        <v>12632</v>
       </c>
       <c r="J273" t="n">
-        <v>21371</v>
+        <v>21913</v>
       </c>
       <c r="K273" t="n">
         <v>26</v>
@@ -11820,7 +11820,7 @@
         <v>35</v>
       </c>
       <c r="M273" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="274">
@@ -11846,22 +11846,22 @@
         <v>100</v>
       </c>
       <c r="H274" t="n">
-        <v>9097</v>
+        <v>9329</v>
       </c>
       <c r="I274" t="n">
-        <v>12411</v>
+        <v>12727</v>
       </c>
       <c r="J274" t="n">
-        <v>21509</v>
+        <v>22056</v>
       </c>
       <c r="K274" t="n">
         <v>26</v>
       </c>
       <c r="L274" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M274" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="275">
@@ -11887,22 +11887,22 @@
         <v>100</v>
       </c>
       <c r="H275" t="n">
-        <v>9084</v>
+        <v>9317</v>
       </c>
       <c r="I275" t="n">
-        <v>12300</v>
+        <v>12614</v>
       </c>
       <c r="J275" t="n">
-        <v>21384</v>
+        <v>21931</v>
       </c>
       <c r="K275" t="n">
         <v>26</v>
       </c>
       <c r="L275" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M275" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="276">
@@ -11928,13 +11928,13 @@
         <v>100</v>
       </c>
       <c r="H276" t="n">
-        <v>9069</v>
+        <v>9301</v>
       </c>
       <c r="I276" t="n">
-        <v>12382</v>
+        <v>12698</v>
       </c>
       <c r="J276" t="n">
-        <v>21451</v>
+        <v>21999</v>
       </c>
       <c r="K276" t="n">
         <v>26</v>
@@ -11943,7 +11943,7 @@
         <v>36</v>
       </c>
       <c r="M276" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="277">
@@ -11969,19 +11969,19 @@
         <v>100</v>
       </c>
       <c r="H277" t="n">
-        <v>9136</v>
+        <v>9370</v>
       </c>
       <c r="I277" t="n">
-        <v>12441</v>
+        <v>12759</v>
       </c>
       <c r="J277" t="n">
-        <v>21577</v>
+        <v>22129</v>
       </c>
       <c r="K277" t="n">
         <v>27</v>
       </c>
       <c r="L277" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M277" t="n">
         <v>63</v>
@@ -12010,22 +12010,22 @@
         <v>100</v>
       </c>
       <c r="H278" t="n">
-        <v>9229</v>
+        <v>9466</v>
       </c>
       <c r="I278" t="n">
-        <v>12362</v>
+        <v>12679</v>
       </c>
       <c r="J278" t="n">
-        <v>21591</v>
+        <v>22144</v>
       </c>
       <c r="K278" t="n">
         <v>27</v>
       </c>
       <c r="L278" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M278" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="279">
@@ -12051,13 +12051,13 @@
         <v>100</v>
       </c>
       <c r="H279" t="n">
-        <v>9201</v>
+        <v>9437</v>
       </c>
       <c r="I279" t="n">
-        <v>12476</v>
+        <v>12795</v>
       </c>
       <c r="J279" t="n">
-        <v>21677</v>
+        <v>22233</v>
       </c>
       <c r="K279" t="n">
         <v>27</v>
@@ -12066,7 +12066,7 @@
         <v>37</v>
       </c>
       <c r="M279" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="280">
@@ -12092,19 +12092,19 @@
         <v>100</v>
       </c>
       <c r="H280" t="n">
-        <v>9264</v>
+        <v>9501</v>
       </c>
       <c r="I280" t="n">
-        <v>12558</v>
+        <v>12880</v>
       </c>
       <c r="J280" t="n">
-        <v>21821</v>
+        <v>22381</v>
       </c>
       <c r="K280" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L280" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M280" t="n">
         <v>65</v>
@@ -12133,22 +12133,22 @@
         <v>100</v>
       </c>
       <c r="H281" t="n">
-        <v>9049</v>
+        <v>9280</v>
       </c>
       <c r="I281" t="n">
-        <v>12187</v>
+        <v>12500</v>
       </c>
       <c r="J281" t="n">
-        <v>21236</v>
+        <v>21780</v>
       </c>
       <c r="K281" t="n">
         <v>27</v>
       </c>
       <c r="L281" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M281" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="282">
@@ -12174,13 +12174,13 @@
         <v>100</v>
       </c>
       <c r="H282" t="n">
-        <v>8972</v>
+        <v>9201</v>
       </c>
       <c r="I282" t="n">
-        <v>12233</v>
+        <v>12546</v>
       </c>
       <c r="J282" t="n">
-        <v>21205</v>
+        <v>21747</v>
       </c>
       <c r="K282" t="n">
         <v>27</v>
@@ -12189,7 +12189,7 @@
         <v>37</v>
       </c>
       <c r="M282" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="283">
@@ -12215,13 +12215,13 @@
         <v>100</v>
       </c>
       <c r="H283" t="n">
-        <v>8904</v>
+        <v>9132</v>
       </c>
       <c r="I283" t="n">
-        <v>12525</v>
+        <v>12845</v>
       </c>
       <c r="J283" t="n">
-        <v>21429</v>
+        <v>21977</v>
       </c>
       <c r="K283" t="n">
         <v>27</v>
@@ -12230,7 +12230,7 @@
         <v>38</v>
       </c>
       <c r="M283" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="284">
@@ -12256,22 +12256,22 @@
         <v>100</v>
       </c>
       <c r="H284" t="n">
-        <v>8665</v>
+        <v>8886</v>
       </c>
       <c r="I284" t="n">
-        <v>11157</v>
+        <v>11442</v>
       </c>
       <c r="J284" t="n">
-        <v>19823</v>
+        <v>20328</v>
       </c>
       <c r="K284" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L284" t="n">
         <v>34</v>
       </c>
       <c r="M284" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="285">
@@ -12297,22 +12297,22 @@
         <v>100</v>
       </c>
       <c r="H285" t="n">
-        <v>8536</v>
+        <v>8754</v>
       </c>
       <c r="I285" t="n">
-        <v>11243</v>
+        <v>11529</v>
       </c>
       <c r="J285" t="n">
-        <v>19779</v>
+        <v>20282</v>
       </c>
       <c r="K285" t="n">
         <v>26</v>
       </c>
       <c r="L285" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M285" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="286">
@@ -12338,22 +12338,22 @@
         <v>100</v>
       </c>
       <c r="H286" t="n">
-        <v>8391</v>
+        <v>8604</v>
       </c>
       <c r="I286" t="n">
-        <v>11311</v>
+        <v>11597</v>
       </c>
       <c r="J286" t="n">
-        <v>19702</v>
+        <v>20201</v>
       </c>
       <c r="K286" t="n">
         <v>26</v>
       </c>
       <c r="L286" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M286" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="287">
@@ -12379,13 +12379,13 @@
         <v>100</v>
       </c>
       <c r="H287" t="n">
-        <v>8208</v>
+        <v>8417</v>
       </c>
       <c r="I287" t="n">
-        <v>11417</v>
+        <v>11707</v>
       </c>
       <c r="J287" t="n">
-        <v>19625</v>
+        <v>20123</v>
       </c>
       <c r="K287" t="n">
         <v>25</v>
@@ -12394,7 +12394,7 @@
         <v>35</v>
       </c>
       <c r="M287" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="288">
@@ -12420,19 +12420,19 @@
         <v>100</v>
       </c>
       <c r="H288" t="n">
-        <v>8224</v>
+        <v>8430</v>
       </c>
       <c r="I288" t="n">
-        <v>11496</v>
+        <v>11785</v>
       </c>
       <c r="J288" t="n">
-        <v>19720</v>
+        <v>20215</v>
       </c>
       <c r="K288" t="n">
         <v>25</v>
       </c>
       <c r="L288" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M288" t="n">
         <v>61</v>
@@ -12461,13 +12461,13 @@
         <v>100</v>
       </c>
       <c r="H289" t="n">
-        <v>8114</v>
+        <v>8317</v>
       </c>
       <c r="I289" t="n">
-        <v>11546</v>
+        <v>11835</v>
       </c>
       <c r="J289" t="n">
-        <v>19661</v>
+        <v>20152</v>
       </c>
       <c r="K289" t="n">
         <v>25</v>
@@ -12502,13 +12502,13 @@
         <v>100</v>
       </c>
       <c r="H290" t="n">
-        <v>7990</v>
+        <v>8188</v>
       </c>
       <c r="I290" t="n">
-        <v>11626</v>
+        <v>11915</v>
       </c>
       <c r="J290" t="n">
-        <v>19615</v>
+        <v>20103</v>
       </c>
       <c r="K290" t="n">
         <v>25</v>
@@ -12543,13 +12543,13 @@
         <v>100</v>
       </c>
       <c r="H291" t="n">
-        <v>7885</v>
+        <v>8079</v>
       </c>
       <c r="I291" t="n">
-        <v>11712</v>
+        <v>12001</v>
       </c>
       <c r="J291" t="n">
-        <v>19597</v>
+        <v>20080</v>
       </c>
       <c r="K291" t="n">
         <v>24</v>
@@ -12558,7 +12558,7 @@
         <v>36</v>
       </c>
       <c r="M291" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="292">
@@ -12584,19 +12584,19 @@
         <v>100</v>
       </c>
       <c r="H292" t="n">
-        <v>7892</v>
+        <v>8086</v>
       </c>
       <c r="I292" t="n">
-        <v>11801</v>
+        <v>12091</v>
       </c>
       <c r="J292" t="n">
-        <v>19694</v>
+        <v>20177</v>
       </c>
       <c r="K292" t="n">
         <v>24</v>
       </c>
       <c r="L292" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M292" t="n">
         <v>61</v>
@@ -12625,13 +12625,13 @@
         <v>100</v>
       </c>
       <c r="H293" t="n">
-        <v>7798</v>
+        <v>7988</v>
       </c>
       <c r="I293" t="n">
-        <v>11890</v>
+        <v>12179</v>
       </c>
       <c r="J293" t="n">
-        <v>19688</v>
+        <v>20166</v>
       </c>
       <c r="K293" t="n">
         <v>24</v>
@@ -12666,13 +12666,13 @@
         <v>100</v>
       </c>
       <c r="H294" t="n">
-        <v>7658</v>
+        <v>7842</v>
       </c>
       <c r="I294" t="n">
-        <v>11916</v>
+        <v>12203</v>
       </c>
       <c r="J294" t="n">
-        <v>19573</v>
+        <v>20045</v>
       </c>
       <c r="K294" t="n">
         <v>24</v>
@@ -12707,13 +12707,13 @@
         <v>100</v>
       </c>
       <c r="H295" t="n">
-        <v>7484</v>
+        <v>7663</v>
       </c>
       <c r="I295" t="n">
-        <v>11980</v>
+        <v>12266</v>
       </c>
       <c r="J295" t="n">
-        <v>19464</v>
+        <v>19928</v>
       </c>
       <c r="K295" t="n">
         <v>23</v>
@@ -12748,13 +12748,13 @@
         <v>100</v>
       </c>
       <c r="H296" t="n">
-        <v>7370</v>
+        <v>7544</v>
       </c>
       <c r="I296" t="n">
-        <v>12038</v>
+        <v>12322</v>
       </c>
       <c r="J296" t="n">
-        <v>19407</v>
+        <v>19866</v>
       </c>
       <c r="K296" t="n">
         <v>23</v>
@@ -12763,7 +12763,7 @@
         <v>37</v>
       </c>
       <c r="M296" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="297">
@@ -12789,13 +12789,13 @@
         <v>100</v>
       </c>
       <c r="H297" t="n">
-        <v>7433</v>
+        <v>7606</v>
       </c>
       <c r="I297" t="n">
-        <v>12066</v>
+        <v>12348</v>
       </c>
       <c r="J297" t="n">
-        <v>19499</v>
+        <v>19954</v>
       </c>
       <c r="K297" t="n">
         <v>23</v>
@@ -12830,13 +12830,13 @@
         <v>100</v>
       </c>
       <c r="H298" t="n">
-        <v>7325</v>
+        <v>7494</v>
       </c>
       <c r="I298" t="n">
-        <v>12152</v>
+        <v>12433</v>
       </c>
       <c r="J298" t="n">
-        <v>19478</v>
+        <v>19927</v>
       </c>
       <c r="K298" t="n">
         <v>22</v>
@@ -12871,13 +12871,13 @@
         <v>100</v>
       </c>
       <c r="H299" t="n">
-        <v>7293</v>
+        <v>7460</v>
       </c>
       <c r="I299" t="n">
-        <v>12226</v>
+        <v>12506</v>
       </c>
       <c r="J299" t="n">
-        <v>19519</v>
+        <v>19966</v>
       </c>
       <c r="K299" t="n">
         <v>22</v>
@@ -12912,13 +12912,13 @@
         <v>100</v>
       </c>
       <c r="H300" t="n">
-        <v>7157</v>
+        <v>7318</v>
       </c>
       <c r="I300" t="n">
-        <v>12286</v>
+        <v>12562</v>
       </c>
       <c r="J300" t="n">
-        <v>19443</v>
+        <v>19880</v>
       </c>
       <c r="K300" t="n">
         <v>22</v>
@@ -12953,13 +12953,13 @@
         <v>100</v>
       </c>
       <c r="H301" t="n">
-        <v>7153</v>
+        <v>7311</v>
       </c>
       <c r="I301" t="n">
-        <v>12384</v>
+        <v>12658</v>
       </c>
       <c r="J301" t="n">
-        <v>19537</v>
+        <v>19969</v>
       </c>
       <c r="K301" t="n">
         <v>22</v>
@@ -12994,13 +12994,13 @@
         <v>100</v>
       </c>
       <c r="H302" t="n">
-        <v>7029</v>
+        <v>7182</v>
       </c>
       <c r="I302" t="n">
-        <v>12504</v>
+        <v>12776</v>
       </c>
       <c r="J302" t="n">
-        <v>19533</v>
+        <v>19958</v>
       </c>
       <c r="K302" t="n">
         <v>21</v>
@@ -13009,7 +13009,7 @@
         <v>38</v>
       </c>
       <c r="M302" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="303">
@@ -13035,13 +13035,13 @@
         <v>100</v>
       </c>
       <c r="H303" t="n">
-        <v>7321</v>
+        <v>7478</v>
       </c>
       <c r="I303" t="n">
-        <v>12613</v>
+        <v>12883</v>
       </c>
       <c r="J303" t="n">
-        <v>19934</v>
+        <v>20360</v>
       </c>
       <c r="K303" t="n">
         <v>22</v>
@@ -13076,13 +13076,13 @@
         <v>100</v>
       </c>
       <c r="H304" t="n">
-        <v>7121</v>
+        <v>7270</v>
       </c>
       <c r="I304" t="n">
-        <v>12738</v>
+        <v>13006</v>
       </c>
       <c r="J304" t="n">
-        <v>19859</v>
+        <v>20276</v>
       </c>
       <c r="K304" t="n">
         <v>22</v>
@@ -13091,7 +13091,7 @@
         <v>39</v>
       </c>
       <c r="M304" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="305">
@@ -13117,13 +13117,13 @@
         <v>100</v>
       </c>
       <c r="H305" t="n">
-        <v>6997</v>
+        <v>7141</v>
       </c>
       <c r="I305" t="n">
-        <v>12783</v>
+        <v>13046</v>
       </c>
       <c r="J305" t="n">
-        <v>19780</v>
+        <v>20187</v>
       </c>
       <c r="K305" t="n">
         <v>21</v>
@@ -13132,7 +13132,7 @@
         <v>39</v>
       </c>
       <c r="M305" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="306">
@@ -13158,22 +13158,22 @@
         <v>100</v>
       </c>
       <c r="H306" t="n">
-        <v>6698</v>
+        <v>6833</v>
       </c>
       <c r="I306" t="n">
-        <v>12856</v>
+        <v>13115</v>
       </c>
       <c r="J306" t="n">
-        <v>19554</v>
+        <v>19949</v>
       </c>
       <c r="K306" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L306" t="n">
         <v>39</v>
       </c>
       <c r="M306" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="307">
@@ -13199,22 +13199,22 @@
         <v>100</v>
       </c>
       <c r="H307" t="n">
-        <v>6940</v>
+        <v>7077</v>
       </c>
       <c r="I307" t="n">
-        <v>12909</v>
+        <v>13163</v>
       </c>
       <c r="J307" t="n">
-        <v>19848</v>
+        <v>20240</v>
       </c>
       <c r="K307" t="n">
         <v>21</v>
       </c>
       <c r="L307" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M307" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="308">
@@ -13240,22 +13240,22 @@
         <v>100</v>
       </c>
       <c r="H308" t="n">
-        <v>6666</v>
+        <v>6794</v>
       </c>
       <c r="I308" t="n">
-        <v>13409</v>
+        <v>13667</v>
       </c>
       <c r="J308" t="n">
-        <v>20075</v>
+        <v>20462</v>
       </c>
       <c r="K308" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L308" t="n">
         <v>41</v>
       </c>
       <c r="M308" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="309">
@@ -13281,13 +13281,13 @@
         <v>100</v>
       </c>
       <c r="H309" t="n">
-        <v>6939</v>
+        <v>7069</v>
       </c>
       <c r="I309" t="n">
-        <v>13257</v>
+        <v>13505</v>
       </c>
       <c r="J309" t="n">
-        <v>20196</v>
+        <v>20575</v>
       </c>
       <c r="K309" t="n">
         <v>21</v>
@@ -13322,13 +13322,13 @@
         <v>100</v>
       </c>
       <c r="H310" t="n">
-        <v>6630</v>
+        <v>6751</v>
       </c>
       <c r="I310" t="n">
-        <v>13330</v>
+        <v>13573</v>
       </c>
       <c r="J310" t="n">
-        <v>19960</v>
+        <v>20324</v>
       </c>
       <c r="K310" t="n">
         <v>20</v>
@@ -13337,7 +13337,7 @@
         <v>41</v>
       </c>
       <c r="M310" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="311">
@@ -13363,13 +13363,13 @@
         <v>100</v>
       </c>
       <c r="H311" t="n">
-        <v>6612</v>
+        <v>6730</v>
       </c>
       <c r="I311" t="n">
-        <v>13340</v>
+        <v>13578</v>
       </c>
       <c r="J311" t="n">
-        <v>19952</v>
+        <v>20308</v>
       </c>
       <c r="K311" t="n">
         <v>20</v>
@@ -13404,13 +13404,13 @@
         <v>100</v>
       </c>
       <c r="H312" t="n">
-        <v>6426</v>
+        <v>6537</v>
       </c>
       <c r="I312" t="n">
-        <v>13417</v>
+        <v>13647</v>
       </c>
       <c r="J312" t="n">
-        <v>19843</v>
+        <v>20184</v>
       </c>
       <c r="K312" t="n">
         <v>20</v>
@@ -13419,7 +13419,7 @@
         <v>42</v>
       </c>
       <c r="M312" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="313">
@@ -13445,17 +13445,23 @@
         <v>100</v>
       </c>
       <c r="H313" t="n">
-        <v>6423</v>
+        <v>6530</v>
       </c>
       <c r="I313" t="n">
-        <v>13514</v>
+        <v>13738</v>
       </c>
       <c r="J313" t="n">
-        <v>19937</v>
-      </c>
-      <c r="K313"/>
-      <c r="L313"/>
-      <c r="M313"/>
+        <v>20267</v>
+      </c>
+      <c r="K313" t="n">
+        <v>20</v>
+      </c>
+      <c r="L313" t="n">
+        <v>42</v>
+      </c>
+      <c r="M313" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="n">
@@ -13480,13 +13486,13 @@
         <v>100</v>
       </c>
       <c r="H314" t="n">
-        <v>6551</v>
+        <v>6655</v>
       </c>
       <c r="I314" t="n">
-        <v>13398</v>
+        <v>13613</v>
       </c>
       <c r="J314" t="n">
-        <v>19949</v>
+        <v>20268</v>
       </c>
       <c r="K314"/>
       <c r="L314"/>
@@ -13515,13 +13521,13 @@
         <v>100</v>
       </c>
       <c r="H315" t="n">
-        <v>6559</v>
+        <v>6659</v>
       </c>
       <c r="I315" t="n">
-        <v>13422</v>
+        <v>13628</v>
       </c>
       <c r="J315" t="n">
-        <v>19980</v>
+        <v>20287</v>
       </c>
       <c r="K315"/>
       <c r="L315"/>
@@ -13550,13 +13556,13 @@
         <v>100</v>
       </c>
       <c r="H316" t="n">
-        <v>6577</v>
+        <v>6674</v>
       </c>
       <c r="I316" t="n">
-        <v>13448</v>
+        <v>13647</v>
       </c>
       <c r="J316" t="n">
-        <v>20025</v>
+        <v>20320</v>
       </c>
       <c r="K316"/>
       <c r="L316"/>
@@ -13585,13 +13591,13 @@
         <v>100</v>
       </c>
       <c r="H317" t="n">
-        <v>6633</v>
+        <v>6726</v>
       </c>
       <c r="I317" t="n">
-        <v>13351</v>
+        <v>13539</v>
       </c>
       <c r="J317" t="n">
-        <v>19984</v>
+        <v>20265</v>
       </c>
       <c r="K317"/>
       <c r="L317"/>
@@ -13620,13 +13626,13 @@
         <v>100</v>
       </c>
       <c r="H318" t="n">
-        <v>6848</v>
+        <v>6940</v>
       </c>
       <c r="I318" t="n">
-        <v>13357</v>
+        <v>13536</v>
       </c>
       <c r="J318" t="n">
-        <v>20205</v>
+        <v>20476</v>
       </c>
       <c r="K318"/>
       <c r="L318"/>
@@ -13655,13 +13661,13 @@
         <v>100</v>
       </c>
       <c r="H319" t="n">
-        <v>6997</v>
+        <v>7086</v>
       </c>
       <c r="I319" t="n">
-        <v>13432</v>
+        <v>13603</v>
       </c>
       <c r="J319" t="n">
-        <v>20430</v>
+        <v>20689</v>
       </c>
       <c r="K319"/>
       <c r="L319"/>
@@ -13690,13 +13696,13 @@
         <v>100</v>
       </c>
       <c r="H320" t="n">
-        <v>6966</v>
+        <v>7049</v>
       </c>
       <c r="I320" t="n">
-        <v>13487</v>
+        <v>13648</v>
       </c>
       <c r="J320" t="n">
-        <v>20452</v>
+        <v>20697</v>
       </c>
       <c r="K320"/>
       <c r="L320"/>
@@ -13725,13 +13731,13 @@
         <v>100</v>
       </c>
       <c r="H321" t="n">
-        <v>6935</v>
+        <v>7013</v>
       </c>
       <c r="I321" t="n">
-        <v>13542</v>
+        <v>13693</v>
       </c>
       <c r="J321" t="n">
-        <v>20477</v>
+        <v>20706</v>
       </c>
       <c r="K321"/>
       <c r="L321"/>
@@ -13760,13 +13766,13 @@
         <v>100</v>
       </c>
       <c r="H322" t="n">
-        <v>6903</v>
+        <v>6975</v>
       </c>
       <c r="I322" t="n">
-        <v>13597</v>
+        <v>13739</v>
       </c>
       <c r="J322" t="n">
-        <v>20500</v>
+        <v>20714</v>
       </c>
       <c r="K322"/>
       <c r="L322"/>
@@ -13795,13 +13801,13 @@
         <v>100</v>
       </c>
       <c r="H323" t="n">
-        <v>6802</v>
+        <v>6869</v>
       </c>
       <c r="I323" t="n">
-        <v>12709</v>
+        <v>12833</v>
       </c>
       <c r="J323" t="n">
-        <v>19512</v>
+        <v>19702</v>
       </c>
       <c r="K323"/>
       <c r="L323"/>
@@ -13830,13 +13836,13 @@
         <v>100</v>
       </c>
       <c r="H324" t="n">
-        <v>6694</v>
+        <v>6753</v>
       </c>
       <c r="I324" t="n">
-        <v>11755</v>
+        <v>11858</v>
       </c>
       <c r="J324" t="n">
-        <v>18448</v>
+        <v>18611</v>
       </c>
       <c r="K324"/>
       <c r="L324"/>
@@ -13865,13 +13871,13 @@
         <v>100</v>
       </c>
       <c r="H325" t="n">
-        <v>6584</v>
+        <v>6636</v>
       </c>
       <c r="I325" t="n">
-        <v>10792</v>
+        <v>10878</v>
       </c>
       <c r="J325" t="n">
-        <v>17376</v>
+        <v>17515</v>
       </c>
       <c r="K325"/>
       <c r="L325"/>
@@ -13900,13 +13906,13 @@
         <v>100</v>
       </c>
       <c r="H326" t="n">
-        <v>6526</v>
+        <v>6573</v>
       </c>
       <c r="I326" t="n">
-        <v>10921</v>
+        <v>10999</v>
       </c>
       <c r="J326" t="n">
-        <v>17447</v>
+        <v>17571</v>
       </c>
       <c r="K326"/>
       <c r="L326"/>
@@ -13935,13 +13941,13 @@
         <v>100</v>
       </c>
       <c r="H327" t="n">
-        <v>6466</v>
+        <v>6506</v>
       </c>
       <c r="I327" t="n">
-        <v>11054</v>
+        <v>11123</v>
       </c>
       <c r="J327" t="n">
-        <v>17520</v>
+        <v>17629</v>
       </c>
       <c r="K327"/>
       <c r="L327"/>
@@ -13970,13 +13976,13 @@
         <v>100</v>
       </c>
       <c r="H328" t="n">
-        <v>6408</v>
+        <v>6442</v>
       </c>
       <c r="I328" t="n">
-        <v>11184</v>
+        <v>11244</v>
       </c>
       <c r="J328" t="n">
-        <v>17593</v>
+        <v>17686</v>
       </c>
       <c r="K328"/>
       <c r="L328"/>
